--- a/research/traditional_assets/database/data/slovenia/slovenia_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_drugs_pharmaceutical.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09823469640632954</v>
+        <v>0.09808450048315751</v>
       </c>
       <c r="C2">
-        <v>4436.967012436802</v>
+        <v>4402.892443744898</v>
       </c>
       <c r="D2">
-        <v>3954.867012436802</v>
+        <v>3965.170443744897</v>
       </c>
       <c r="E2">
-        <v>-12.9</v>
+        <v>31.47799999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44.37799999999999</v>
       </c>
       <c r="G2">
         <v>482.1</v>
@@ -1457,28 +1457,28 @@
         <v>457.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.2322134</v>
       </c>
       <c r="N2">
-        <v>457.3</v>
+        <v>455.0677866</v>
       </c>
       <c r="O2">
-        <v>86.887</v>
+        <v>86.462879454</v>
       </c>
       <c r="P2">
-        <v>370.413</v>
+        <v>368.604907146</v>
       </c>
       <c r="Q2">
-        <v>472.913</v>
+        <v>471.104907146</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09823469640632954</v>
+        <v>0.09866370755874496</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.891358054585045</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>204.8639256443851</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09808450048315751</v>
+        <v>0.09793430455998547</v>
       </c>
       <c r="C3">
-        <v>4402.892443744898</v>
+        <v>4368.87170138614</v>
       </c>
       <c r="D3">
-        <v>3965.170443744897</v>
+        <v>3975.52770138614</v>
       </c>
       <c r="E3">
-        <v>31.47799999999999</v>
+        <v>75.85599999999998</v>
       </c>
       <c r="F3">
-        <v>44.37799999999999</v>
+        <v>88.75599999999999</v>
       </c>
       <c r="G3">
         <v>482.1</v>
@@ -1539,28 +1539,28 @@
         <v>457.3</v>
       </c>
       <c r="M3">
-        <v>2.2322134</v>
+        <v>4.464426799999999</v>
       </c>
       <c r="N3">
-        <v>455.0677866</v>
+        <v>452.8355732</v>
       </c>
       <c r="O3">
-        <v>86.462879454</v>
+        <v>86.03875890800001</v>
       </c>
       <c r="P3">
-        <v>368.604907146</v>
+        <v>366.796814292</v>
       </c>
       <c r="Q3">
-        <v>471.104907146</v>
+        <v>469.296814292</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09866370755874496</v>
+        <v>0.09910147404080151</v>
       </c>
       <c r="T3">
-        <v>0.891358054585045</v>
+        <v>0.8987394263773063</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>204.8639256443851</v>
+        <v>102.4319628221926</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09793430455998547</v>
+        <v>0.09778410863681344</v>
       </c>
       <c r="C4">
-        <v>4368.87170138614</v>
+        <v>4334.905208257775</v>
       </c>
       <c r="D4">
-        <v>3975.52770138614</v>
+        <v>3985.939208257775</v>
       </c>
       <c r="E4">
-        <v>75.85599999999998</v>
+        <v>120.234</v>
       </c>
       <c r="F4">
-        <v>88.75599999999999</v>
+        <v>133.134</v>
       </c>
       <c r="G4">
         <v>482.1</v>
@@ -1621,28 +1621,28 @@
         <v>457.3</v>
       </c>
       <c r="M4">
-        <v>4.464426799999999</v>
+        <v>6.696640199999999</v>
       </c>
       <c r="N4">
-        <v>452.8355732</v>
+        <v>450.6033598</v>
       </c>
       <c r="O4">
-        <v>86.03875890800001</v>
+        <v>85.61463836200001</v>
       </c>
       <c r="P4">
-        <v>366.796814292</v>
+        <v>364.988721438</v>
       </c>
       <c r="Q4">
-        <v>469.296814292</v>
+        <v>467.488721438</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09910147404080151</v>
+        <v>0.09954826663589016</v>
       </c>
       <c r="T4">
-        <v>0.8987394263773063</v>
+        <v>0.9062729914023977</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.4319628221926</v>
+        <v>68.28797521479504</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09778410863681344</v>
+        <v>0.09763391271364143</v>
       </c>
       <c r="C5">
-        <v>4334.905208257775</v>
+        <v>4300.993391698782</v>
       </c>
       <c r="D5">
-        <v>3985.939208257775</v>
+        <v>3996.405391698782</v>
       </c>
       <c r="E5">
-        <v>120.234</v>
+        <v>164.612</v>
       </c>
       <c r="F5">
-        <v>133.134</v>
+        <v>177.512</v>
       </c>
       <c r="G5">
         <v>482.1</v>
@@ -1703,28 +1703,28 @@
         <v>457.3</v>
       </c>
       <c r="M5">
-        <v>6.696640199999999</v>
+        <v>8.928853599999998</v>
       </c>
       <c r="N5">
-        <v>450.6033598</v>
+        <v>448.3711464</v>
       </c>
       <c r="O5">
-        <v>85.61463836200001</v>
+        <v>85.190517816</v>
       </c>
       <c r="P5">
-        <v>364.988721438</v>
+        <v>363.180628584</v>
       </c>
       <c r="Q5">
-        <v>467.488721438</v>
+        <v>465.6806285839999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09954826663589016</v>
+        <v>0.1000043674100431</v>
       </c>
       <c r="T5">
-        <v>0.9062729914023977</v>
+        <v>0.9139635056988451</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.28797521479504</v>
+        <v>51.21598141109628</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09763391271364143</v>
+        <v>0.0974837167904694</v>
       </c>
       <c r="C6">
-        <v>4300.993391698782</v>
+        <v>4267.136683548341</v>
       </c>
       <c r="D6">
-        <v>3996.405391698782</v>
+        <v>4006.926683548342</v>
       </c>
       <c r="E6">
-        <v>164.612</v>
+        <v>208.99</v>
       </c>
       <c r="F6">
-        <v>177.512</v>
+        <v>221.89</v>
       </c>
       <c r="G6">
         <v>482.1</v>
@@ -1785,28 +1785,28 @@
         <v>457.3</v>
       </c>
       <c r="M6">
-        <v>8.928853599999998</v>
+        <v>11.161067</v>
       </c>
       <c r="N6">
-        <v>448.3711464</v>
+        <v>446.138933</v>
       </c>
       <c r="O6">
-        <v>85.190517816</v>
+        <v>84.76639727</v>
       </c>
       <c r="P6">
-        <v>363.180628584</v>
+        <v>361.37253573</v>
       </c>
       <c r="Q6">
-        <v>465.6806285839999</v>
+        <v>463.8725357299999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1000043674100431</v>
+        <v>0.1004700703057573</v>
       </c>
       <c r="T6">
-        <v>0.9139635056988451</v>
+        <v>0.9218159255594283</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.21598141109628</v>
+        <v>40.97278512887702</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0974837167904694</v>
+        <v>0.09733352086729735</v>
       </c>
       <c r="C7">
-        <v>4267.136683548341</v>
+        <v>4233.335520205233</v>
       </c>
       <c r="D7">
-        <v>4006.926683548342</v>
+        <v>4017.503520205233</v>
       </c>
       <c r="E7">
-        <v>208.99</v>
+        <v>253.368</v>
       </c>
       <c r="F7">
-        <v>221.89</v>
+        <v>266.268</v>
       </c>
       <c r="G7">
         <v>482.1</v>
@@ -1867,28 +1867,28 @@
         <v>457.3</v>
       </c>
       <c r="M7">
-        <v>11.161067</v>
+        <v>13.3932804</v>
       </c>
       <c r="N7">
-        <v>446.138933</v>
+        <v>443.9067196</v>
       </c>
       <c r="O7">
-        <v>84.76639727</v>
+        <v>84.342276724</v>
       </c>
       <c r="P7">
-        <v>361.37253573</v>
+        <v>359.564442876</v>
       </c>
       <c r="Q7">
-        <v>463.8725357299999</v>
+        <v>462.064442876</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1004700703057573</v>
+        <v>0.1009456817737206</v>
       </c>
       <c r="T7">
-        <v>0.9218159255594283</v>
+        <v>0.9298354181830026</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.97278512887702</v>
+        <v>34.14398760739752</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09733352086729735</v>
+        <v>0.09718332494412536</v>
       </c>
       <c r="C8">
-        <v>4233.335520205233</v>
+        <v>4199.590342688164</v>
       </c>
       <c r="D8">
-        <v>4017.503520205233</v>
+        <v>4028.136342688164</v>
       </c>
       <c r="E8">
-        <v>253.368</v>
+        <v>297.7459999999999</v>
       </c>
       <c r="F8">
-        <v>266.268</v>
+        <v>310.6459999999999</v>
       </c>
       <c r="G8">
         <v>482.1</v>
@@ -1949,28 +1949,28 @@
         <v>457.3</v>
       </c>
       <c r="M8">
-        <v>13.3932804</v>
+        <v>15.62549379999999</v>
       </c>
       <c r="N8">
-        <v>443.9067196</v>
+        <v>441.6745062</v>
       </c>
       <c r="O8">
-        <v>84.342276724</v>
+        <v>83.918156178</v>
       </c>
       <c r="P8">
-        <v>359.564442876</v>
+        <v>357.756350022</v>
       </c>
       <c r="Q8">
-        <v>462.064442876</v>
+        <v>460.2563500219999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1009456817737206</v>
+        <v>0.1014315214452961</v>
       </c>
       <c r="T8">
-        <v>0.9298354181830026</v>
+        <v>0.9380273730135357</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.14398760739752</v>
+        <v>29.26627509205502</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09718332494412535</v>
+        <v>0.09703312902095333</v>
       </c>
       <c r="C9">
-        <v>4199.590342688165</v>
+        <v>4165.901596697084</v>
       </c>
       <c r="D9">
-        <v>4028.136342688165</v>
+        <v>4038.825596697084</v>
       </c>
       <c r="E9">
-        <v>297.746</v>
+        <v>342.124</v>
       </c>
       <c r="F9">
-        <v>310.646</v>
+        <v>355.0239999999999</v>
       </c>
       <c r="G9">
         <v>482.1</v>
@@ -2031,28 +2031,28 @@
         <v>457.3</v>
       </c>
       <c r="M9">
-        <v>15.6254938</v>
+        <v>17.8577072</v>
       </c>
       <c r="N9">
-        <v>441.6745062</v>
+        <v>439.4422928</v>
       </c>
       <c r="O9">
-        <v>83.918156178</v>
+        <v>83.49403563200001</v>
       </c>
       <c r="P9">
-        <v>357.756350022</v>
+        <v>355.948257168</v>
       </c>
       <c r="Q9">
-        <v>460.2563500219999</v>
+        <v>458.4482571679999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1014315214452961</v>
+        <v>0.1019279228488623</v>
       </c>
       <c r="T9">
-        <v>0.9380273730135357</v>
+        <v>0.9463974138186455</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.26627509205501</v>
+        <v>25.60799070554814</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09703312902095333</v>
+        <v>0.0968829330977813</v>
       </c>
       <c r="C10">
-        <v>4165.901596697084</v>
+        <v>4132.269732675448</v>
       </c>
       <c r="D10">
-        <v>4038.825596697084</v>
+        <v>4049.571732675447</v>
       </c>
       <c r="E10">
-        <v>342.124</v>
+        <v>386.502</v>
       </c>
       <c r="F10">
-        <v>355.0239999999999</v>
+        <v>399.4019999999999</v>
       </c>
       <c r="G10">
         <v>482.1</v>
@@ -2113,28 +2113,28 @@
         <v>457.3</v>
       </c>
       <c r="M10">
-        <v>17.8577072</v>
+        <v>20.0899206</v>
       </c>
       <c r="N10">
-        <v>439.4422928</v>
+        <v>437.2100794</v>
       </c>
       <c r="O10">
-        <v>83.49403563200001</v>
+        <v>83.06991508600001</v>
       </c>
       <c r="P10">
-        <v>355.948257168</v>
+        <v>354.140164314</v>
       </c>
       <c r="Q10">
-        <v>458.4482571679999</v>
+        <v>456.6401643139999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1019279228488623</v>
+        <v>0.102435234173386</v>
       </c>
       <c r="T10">
-        <v>0.9463974138186455</v>
+        <v>0.9549514115645267</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.60799070554814</v>
+        <v>22.76265840493168</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0968829330977813</v>
+        <v>0.09673273717460927</v>
       </c>
       <c r="C11">
-        <v>4132.269732675448</v>
+        <v>4098.695205873491</v>
       </c>
       <c r="D11">
-        <v>4049.571732675447</v>
+        <v>4060.375205873491</v>
       </c>
       <c r="E11">
-        <v>386.502</v>
+        <v>430.8799999999999</v>
       </c>
       <c r="F11">
-        <v>399.4019999999999</v>
+        <v>443.7799999999999</v>
       </c>
       <c r="G11">
         <v>482.1</v>
@@ -2195,28 +2195,28 @@
         <v>457.3</v>
       </c>
       <c r="M11">
-        <v>20.0899206</v>
+        <v>22.32213399999999</v>
       </c>
       <c r="N11">
-        <v>437.2100794</v>
+        <v>434.977866</v>
       </c>
       <c r="O11">
-        <v>83.06991508600001</v>
+        <v>82.64579454</v>
       </c>
       <c r="P11">
-        <v>354.140164314</v>
+        <v>352.33207146</v>
       </c>
       <c r="Q11">
-        <v>456.6401643139999</v>
+        <v>454.83207146</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.102435234173386</v>
+        <v>0.1029538190828992</v>
       </c>
       <c r="T11">
-        <v>0.9549514115645267</v>
+        <v>0.9636954981492056</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.76265840493168</v>
+        <v>20.48639256443851</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09673273717460927</v>
+        <v>0.09658254125143724</v>
       </c>
       <c r="C12">
-        <v>4098.695205873491</v>
+        <v>4065.178476412526</v>
       </c>
       <c r="D12">
-        <v>4060.375205873491</v>
+        <v>4071.236476412526</v>
       </c>
       <c r="E12">
-        <v>430.88</v>
+        <v>475.2579999999999</v>
       </c>
       <c r="F12">
-        <v>443.78</v>
+        <v>488.1579999999999</v>
       </c>
       <c r="G12">
         <v>482.1</v>
@@ -2277,28 +2277,28 @@
         <v>457.3</v>
       </c>
       <c r="M12">
-        <v>22.322134</v>
+        <v>24.55434739999999</v>
       </c>
       <c r="N12">
-        <v>434.977866</v>
+        <v>432.7456526</v>
       </c>
       <c r="O12">
-        <v>82.64579454</v>
+        <v>82.221673994</v>
       </c>
       <c r="P12">
-        <v>352.33207146</v>
+        <v>350.523978606</v>
       </c>
       <c r="Q12">
-        <v>454.83207146</v>
+        <v>453.023978606</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1029538190828992</v>
+        <v>0.1034840575858845</v>
       </c>
       <c r="T12">
-        <v>0.9636954981492056</v>
+        <v>0.9726360810616298</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.48639256443851</v>
+        <v>18.62399324039865</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09658254125143724</v>
+        <v>0.09643234532826521</v>
       </c>
       <c r="C13">
-        <v>4065.178476412526</v>
+        <v>4031.720009350262</v>
       </c>
       <c r="D13">
-        <v>4071.236476412526</v>
+        <v>4082.156009350263</v>
       </c>
       <c r="E13">
-        <v>475.2579999999999</v>
+        <v>519.636</v>
       </c>
       <c r="F13">
-        <v>488.1579999999999</v>
+        <v>532.5359999999999</v>
       </c>
       <c r="G13">
         <v>482.1</v>
@@ -2359,28 +2359,28 @@
         <v>457.3</v>
       </c>
       <c r="M13">
-        <v>24.55434739999999</v>
+        <v>26.7865608</v>
       </c>
       <c r="N13">
-        <v>432.7456526</v>
+        <v>430.5134392</v>
       </c>
       <c r="O13">
-        <v>82.221673994</v>
+        <v>81.797553448</v>
       </c>
       <c r="P13">
-        <v>350.523978606</v>
+        <v>348.715885752</v>
       </c>
       <c r="Q13">
-        <v>453.023978606</v>
+        <v>451.2158857519999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1034840575858845</v>
+        <v>0.1040263469639377</v>
       </c>
       <c r="T13">
-        <v>0.9726360810616298</v>
+        <v>0.9817798590402456</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.62399324039865</v>
+        <v>17.07199380369876</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09643234532826521</v>
+        <v>0.09628214940509319</v>
       </c>
       <c r="C14">
-        <v>4031.720009350262</v>
+        <v>3998.320274747183</v>
       </c>
       <c r="D14">
-        <v>4082.156009350263</v>
+        <v>4093.134274747183</v>
       </c>
       <c r="E14">
-        <v>519.636</v>
+        <v>564.0139999999999</v>
       </c>
       <c r="F14">
-        <v>532.5359999999999</v>
+        <v>576.9139999999999</v>
       </c>
       <c r="G14">
         <v>482.1</v>
@@ -2441,28 +2441,28 @@
         <v>457.3</v>
       </c>
       <c r="M14">
-        <v>26.7865608</v>
+        <v>29.01877419999999</v>
       </c>
       <c r="N14">
-        <v>430.5134392</v>
+        <v>428.2812258</v>
       </c>
       <c r="O14">
-        <v>81.797553448</v>
+        <v>81.373432902</v>
       </c>
       <c r="P14">
-        <v>348.715885752</v>
+        <v>346.907792898</v>
       </c>
       <c r="Q14">
-        <v>451.2158857519999</v>
+        <v>449.407792898</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1040263469639377</v>
+        <v>0.1045811027644749</v>
       </c>
       <c r="T14">
-        <v>0.9817798590402456</v>
+        <v>0.9911338388114733</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.07199380369876</v>
+        <v>15.75876351110655</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09628214940509319</v>
+        <v>0.09613195348192118</v>
       </c>
       <c r="C15">
-        <v>3998.320274747183</v>
+        <v>3964.979747733998</v>
       </c>
       <c r="D15">
-        <v>4093.134274747183</v>
+        <v>4104.171747733997</v>
       </c>
       <c r="E15">
-        <v>564.0139999999999</v>
+        <v>608.3919999999999</v>
       </c>
       <c r="F15">
-        <v>576.9139999999999</v>
+        <v>621.2919999999999</v>
       </c>
       <c r="G15">
         <v>482.1</v>
@@ -2523,28 +2523,28 @@
         <v>457.3</v>
       </c>
       <c r="M15">
-        <v>29.01877419999999</v>
+        <v>31.25098759999999</v>
       </c>
       <c r="N15">
-        <v>428.2812258</v>
+        <v>426.0490124</v>
       </c>
       <c r="O15">
-        <v>81.373432902</v>
+        <v>80.94931235600001</v>
       </c>
       <c r="P15">
-        <v>346.907792898</v>
+        <v>345.099700044</v>
       </c>
       <c r="Q15">
-        <v>449.407792898</v>
+        <v>447.599700044</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1045811027644749</v>
+        <v>0.105148759862699</v>
       </c>
       <c r="T15">
-        <v>0.9911338388114733</v>
+        <v>1.000705352995985</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.75876351110655</v>
+        <v>14.63313754602751</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09613195348192118</v>
+        <v>0.09598175755874913</v>
       </c>
       <c r="C16">
-        <v>3964.979747733998</v>
+        <v>3931.698908580191</v>
       </c>
       <c r="D16">
-        <v>4104.171747733997</v>
+        <v>4115.26890858019</v>
       </c>
       <c r="E16">
-        <v>608.3919999999999</v>
+        <v>652.77</v>
       </c>
       <c r="F16">
-        <v>621.2919999999999</v>
+        <v>665.67</v>
       </c>
       <c r="G16">
         <v>482.1</v>
@@ -2605,28 +2605,28 @@
         <v>457.3</v>
       </c>
       <c r="M16">
-        <v>31.25098759999999</v>
+        <v>33.48320099999999</v>
       </c>
       <c r="N16">
-        <v>426.0490124</v>
+        <v>423.816799</v>
       </c>
       <c r="O16">
-        <v>80.94931235600001</v>
+        <v>80.52519181</v>
       </c>
       <c r="P16">
-        <v>345.099700044</v>
+        <v>343.29160719</v>
       </c>
       <c r="Q16">
-        <v>447.599700044</v>
+        <v>445.79160719</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.105148759862699</v>
+        <v>0.1057297735985284</v>
       </c>
       <c r="T16">
-        <v>1.000705352995985</v>
+        <v>1.010502079278957</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.63313754602751</v>
+        <v>13.65759504295901</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09598175755874913</v>
+        <v>0.09602596163557711</v>
       </c>
       <c r="C17">
-        <v>3931.698908580191</v>
+        <v>3884.048682584413</v>
       </c>
       <c r="D17">
-        <v>4115.26890858019</v>
+        <v>4111.996682584412</v>
       </c>
       <c r="E17">
-        <v>652.7699999999999</v>
+        <v>697.1479999999999</v>
       </c>
       <c r="F17">
-        <v>665.6699999999998</v>
+        <v>710.0479999999999</v>
       </c>
       <c r="G17">
         <v>482.1</v>
@@ -2687,45 +2687,45 @@
         <v>457.3</v>
       </c>
       <c r="M17">
-        <v>33.48320099999999</v>
+        <v>36.78048639999999</v>
       </c>
       <c r="N17">
-        <v>423.816799</v>
+        <v>420.5195136</v>
       </c>
       <c r="O17">
-        <v>80.52519181</v>
+        <v>79.89870758400001</v>
       </c>
       <c r="P17">
-        <v>343.29160719</v>
+        <v>340.620806016</v>
       </c>
       <c r="Q17">
-        <v>445.79160719</v>
+        <v>443.120806016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1057297735985284</v>
+        <v>0.1063246209947347</v>
       </c>
       <c r="T17">
-        <v>1.010502079278957</v>
+        <v>1.020532060949617</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.65759504295901</v>
+        <v>12.43322328657405</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09602596163557711</v>
+        <v>0.0958879157124051</v>
       </c>
       <c r="C18">
-        <v>3884.048682584413</v>
+        <v>3849.906884766085</v>
       </c>
       <c r="D18">
-        <v>4111.996682584412</v>
+        <v>4122.232884766085</v>
       </c>
       <c r="E18">
-        <v>697.1479999999999</v>
+        <v>741.526</v>
       </c>
       <c r="F18">
-        <v>710.0479999999999</v>
+        <v>754.4259999999999</v>
       </c>
       <c r="G18">
         <v>482.1</v>
@@ -2769,28 +2769,28 @@
         <v>457.3</v>
       </c>
       <c r="M18">
-        <v>36.78048639999999</v>
+        <v>39.07926679999999</v>
       </c>
       <c r="N18">
-        <v>420.5195136</v>
+        <v>418.2207332</v>
       </c>
       <c r="O18">
-        <v>79.89870758400001</v>
+        <v>79.46193930800001</v>
       </c>
       <c r="P18">
-        <v>340.620806016</v>
+        <v>338.758793892</v>
       </c>
       <c r="Q18">
-        <v>443.120806016</v>
+        <v>441.258793892</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1063246209947347</v>
+        <v>0.1069338020631387</v>
       </c>
       <c r="T18">
-        <v>1.020532060949617</v>
+        <v>1.030803728925596</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.43322328657405</v>
+        <v>11.70185721089322</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0958879157124051</v>
+        <v>0.09574986978923306</v>
       </c>
       <c r="C19">
-        <v>3849.906884766085</v>
+        <v>3815.816177125064</v>
       </c>
       <c r="D19">
-        <v>4122.232884766085</v>
+        <v>4132.520177125064</v>
       </c>
       <c r="E19">
-        <v>741.526</v>
+        <v>785.904</v>
       </c>
       <c r="F19">
-        <v>754.4259999999999</v>
+        <v>798.804</v>
       </c>
       <c r="G19">
         <v>482.1</v>
@@ -2851,28 +2851,28 @@
         <v>457.3</v>
       </c>
       <c r="M19">
-        <v>39.07926679999999</v>
+        <v>41.3780472</v>
       </c>
       <c r="N19">
-        <v>418.2207332</v>
+        <v>415.9219528</v>
       </c>
       <c r="O19">
-        <v>79.46193930800001</v>
+        <v>79.025171032</v>
       </c>
       <c r="P19">
-        <v>338.758793892</v>
+        <v>336.896781768</v>
       </c>
       <c r="Q19">
-        <v>441.258793892</v>
+        <v>439.3967817679999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1069338020631387</v>
+        <v>0.1075578412063818</v>
       </c>
       <c r="T19">
-        <v>1.030803728925596</v>
+        <v>1.041325925388792</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.70185721089322</v>
+        <v>11.05175403251026</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09574986978923306</v>
+        <v>0.09561182386606103</v>
       </c>
       <c r="C20">
-        <v>3815.816177125064</v>
+        <v>3781.776943114568</v>
       </c>
       <c r="D20">
-        <v>4132.520177125064</v>
+        <v>4142.858943114567</v>
       </c>
       <c r="E20">
-        <v>785.9039999999999</v>
+        <v>830.2819999999999</v>
       </c>
       <c r="F20">
-        <v>798.8039999999999</v>
+        <v>843.1819999999999</v>
       </c>
       <c r="G20">
         <v>482.1</v>
@@ -2933,28 +2933,28 @@
         <v>457.3</v>
       </c>
       <c r="M20">
-        <v>41.37804719999999</v>
+        <v>43.6768276</v>
       </c>
       <c r="N20">
-        <v>415.9219528</v>
+        <v>413.6231724</v>
       </c>
       <c r="O20">
-        <v>79.025171032</v>
+        <v>78.58840275600001</v>
       </c>
       <c r="P20">
-        <v>336.896781768</v>
+        <v>335.0347696440001</v>
       </c>
       <c r="Q20">
-        <v>439.396781768</v>
+        <v>437.534769644</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1075578412063818</v>
+        <v>0.1081972887235321</v>
       </c>
       <c r="T20">
-        <v>1.041325925388792</v>
+        <v>1.052107929172068</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.05175403251027</v>
+        <v>10.4700827676413</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09561182386606103</v>
+        <v>0.09547377794288903</v>
       </c>
       <c r="C21">
-        <v>3781.776943114568</v>
+        <v>3747.789570034738</v>
       </c>
       <c r="D21">
-        <v>4142.858943114567</v>
+        <v>4153.249570034737</v>
       </c>
       <c r="E21">
-        <v>830.2819999999999</v>
+        <v>874.66</v>
       </c>
       <c r="F21">
-        <v>843.1819999999999</v>
+        <v>887.5599999999999</v>
       </c>
       <c r="G21">
         <v>482.1</v>
@@ -3015,28 +3015,28 @@
         <v>457.3</v>
       </c>
       <c r="M21">
-        <v>43.6768276</v>
+        <v>45.97560799999999</v>
       </c>
       <c r="N21">
-        <v>413.6231724</v>
+        <v>411.324392</v>
       </c>
       <c r="O21">
-        <v>78.58840275600001</v>
+        <v>78.15163448</v>
       </c>
       <c r="P21">
-        <v>335.0347696440001</v>
+        <v>333.17275752</v>
       </c>
       <c r="Q21">
-        <v>437.534769644</v>
+        <v>435.6727575199999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1081972887235321</v>
+        <v>0.1088527224286113</v>
       </c>
       <c r="T21">
-        <v>1.052107929172068</v>
+        <v>1.063159483049926</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.4700827676413</v>
+        <v>9.946578629259237</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09547377794288903</v>
+        <v>0.09562490201971699</v>
       </c>
       <c r="C22">
-        <v>3747.789570034738</v>
+        <v>3692.039254402452</v>
       </c>
       <c r="D22">
-        <v>4153.249570034737</v>
+        <v>4141.877254402451</v>
       </c>
       <c r="E22">
-        <v>874.66</v>
+        <v>919.038</v>
       </c>
       <c r="F22">
-        <v>887.5599999999999</v>
+        <v>931.938</v>
       </c>
       <c r="G22">
         <v>482.1</v>
@@ -3097,45 +3097,45 @@
         <v>457.3</v>
       </c>
       <c r="M22">
-        <v>45.97560799999999</v>
+        <v>49.858683</v>
       </c>
       <c r="N22">
-        <v>411.324392</v>
+        <v>407.441317</v>
       </c>
       <c r="O22">
-        <v>78.15163448</v>
+        <v>77.41385023000001</v>
       </c>
       <c r="P22">
-        <v>333.17275752</v>
+        <v>330.02746677</v>
       </c>
       <c r="Q22">
-        <v>435.6727575199999</v>
+        <v>432.52746677</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1088527224286113</v>
+        <v>0.1095247493920468</v>
       </c>
       <c r="T22">
-        <v>1.063159483049926</v>
+        <v>1.074490823101907</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.946578629259237</v>
+        <v>9.171922972774873</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09562490201971699</v>
+        <v>0.09550062609654497</v>
       </c>
       <c r="C23">
-        <v>3692.039254402452</v>
+        <v>3657.008646255731</v>
       </c>
       <c r="D23">
-        <v>4141.877254402451</v>
+        <v>4151.22464625573</v>
       </c>
       <c r="E23">
-        <v>919.0379999999998</v>
+        <v>963.4159999999998</v>
       </c>
       <c r="F23">
-        <v>931.9379999999998</v>
+        <v>976.3159999999998</v>
       </c>
       <c r="G23">
         <v>482.1</v>
@@ -3179,28 +3179,28 @@
         <v>457.3</v>
       </c>
       <c r="M23">
-        <v>49.85868299999998</v>
+        <v>52.23290599999999</v>
       </c>
       <c r="N23">
-        <v>407.441317</v>
+        <v>405.067094</v>
       </c>
       <c r="O23">
-        <v>77.41385023000001</v>
+        <v>76.96274786000001</v>
       </c>
       <c r="P23">
-        <v>330.02746677</v>
+        <v>328.10434614</v>
       </c>
       <c r="Q23">
-        <v>432.52746677</v>
+        <v>430.6043461399999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1095247493920468</v>
+        <v>0.1102140078160833</v>
       </c>
       <c r="T23">
-        <v>1.074490823101907</v>
+        <v>1.086112710334708</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.171922972774876</v>
+        <v>8.75501738310329</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09550062609654497</v>
+        <v>0.09537635017337294</v>
       </c>
       <c r="C24">
-        <v>3657.008646255731</v>
+        <v>3622.020323942323</v>
       </c>
       <c r="D24">
-        <v>4151.22464625573</v>
+        <v>4160.614323942323</v>
       </c>
       <c r="E24">
-        <v>963.4159999999998</v>
+        <v>1007.794</v>
       </c>
       <c r="F24">
-        <v>976.3159999999998</v>
+        <v>1020.694</v>
       </c>
       <c r="G24">
         <v>482.1</v>
@@ -3261,28 +3261,28 @@
         <v>457.3</v>
       </c>
       <c r="M24">
-        <v>52.23290599999999</v>
+        <v>54.60712899999999</v>
       </c>
       <c r="N24">
-        <v>405.067094</v>
+        <v>402.692871</v>
       </c>
       <c r="O24">
-        <v>76.96274786000001</v>
+        <v>76.51164549000001</v>
       </c>
       <c r="P24">
-        <v>328.10434614</v>
+        <v>326.18122551</v>
       </c>
       <c r="Q24">
-        <v>430.6043461399999</v>
+        <v>428.6812255099999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1102140078160833</v>
+        <v>0.1109211690563285</v>
       </c>
       <c r="T24">
-        <v>1.086112710334708</v>
+        <v>1.098036464768361</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.75501738310329</v>
+        <v>8.374364453403146</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09537635017337294</v>
+        <v>0.09525207425020092</v>
       </c>
       <c r="C25">
-        <v>3622.020323942323</v>
+        <v>3587.074575052397</v>
       </c>
       <c r="D25">
-        <v>4160.614323942323</v>
+        <v>4170.046575052396</v>
       </c>
       <c r="E25">
-        <v>1007.794</v>
+        <v>1052.172</v>
       </c>
       <c r="F25">
-        <v>1020.694</v>
+        <v>1065.072</v>
       </c>
       <c r="G25">
         <v>482.1</v>
@@ -3343,28 +3343,28 @@
         <v>457.3</v>
       </c>
       <c r="M25">
-        <v>54.60712899999999</v>
+        <v>56.98135199999999</v>
       </c>
       <c r="N25">
-        <v>402.692871</v>
+        <v>400.318648</v>
       </c>
       <c r="O25">
-        <v>76.51164549000001</v>
+        <v>76.06054312000001</v>
       </c>
       <c r="P25">
-        <v>326.18122551</v>
+        <v>324.25810488</v>
       </c>
       <c r="Q25">
-        <v>428.6812255099999</v>
+        <v>426.75810488</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1109211690563285</v>
+        <v>0.1116469398028959</v>
       </c>
       <c r="T25">
-        <v>1.098036464768361</v>
+        <v>1.110274002213426</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.374364453403146</v>
+        <v>8.025432601178014</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09525207425020092</v>
+        <v>0.09512779832702889</v>
       </c>
       <c r="C26">
-        <v>3587.074575052397</v>
+        <v>3552.171689789961</v>
       </c>
       <c r="D26">
-        <v>4170.046575052396</v>
+        <v>4179.52168978996</v>
       </c>
       <c r="E26">
-        <v>1052.172</v>
+        <v>1096.55</v>
       </c>
       <c r="F26">
-        <v>1065.072</v>
+        <v>1109.45</v>
       </c>
       <c r="G26">
         <v>482.1</v>
@@ -3425,28 +3425,28 @@
         <v>457.3</v>
       </c>
       <c r="M26">
-        <v>56.98135199999999</v>
+        <v>59.35557499999999</v>
       </c>
       <c r="N26">
-        <v>400.318648</v>
+        <v>397.944425</v>
       </c>
       <c r="O26">
-        <v>76.06054312000001</v>
+        <v>75.60944075</v>
       </c>
       <c r="P26">
-        <v>324.25810488</v>
+        <v>322.33498425</v>
       </c>
       <c r="Q26">
-        <v>426.75810488</v>
+        <v>424.83498425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1116469398028959</v>
+        <v>0.1123920644360385</v>
       </c>
       <c r="T26">
-        <v>1.110274002213426</v>
+        <v>1.122837873990359</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.025432601178014</v>
+        <v>7.704415297130895</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09512779832702889</v>
+        <v>0.09517200240385684</v>
       </c>
       <c r="C27">
-        <v>3552.171689789961</v>
+        <v>3504.4185277536</v>
       </c>
       <c r="D27">
-        <v>4179.52168978996</v>
+        <v>4176.146527753599</v>
       </c>
       <c r="E27">
-        <v>1096.55</v>
+        <v>1140.928</v>
       </c>
       <c r="F27">
-        <v>1109.45</v>
+        <v>1153.828</v>
       </c>
       <c r="G27">
         <v>482.1</v>
@@ -3507,45 +3507,45 @@
         <v>457.3</v>
       </c>
       <c r="M27">
-        <v>59.35557499999999</v>
+        <v>62.65286039999999</v>
       </c>
       <c r="N27">
-        <v>397.944425</v>
+        <v>394.6471396</v>
       </c>
       <c r="O27">
-        <v>75.60944075</v>
+        <v>74.982956524</v>
       </c>
       <c r="P27">
-        <v>322.33498425</v>
+        <v>319.664183076</v>
       </c>
       <c r="Q27">
-        <v>424.83498425</v>
+        <v>422.1641830759999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1123920644360385</v>
+        <v>0.1131573275727795</v>
       </c>
       <c r="T27">
-        <v>1.122837873990359</v>
+        <v>1.135741309869371</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.704415297130895</v>
+        <v>7.298948477059478</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09517200240385684</v>
+        <v>0.09505420648068483</v>
       </c>
       <c r="C28">
-        <v>3504.4185277536</v>
+        <v>3469.046846282134</v>
       </c>
       <c r="D28">
-        <v>4176.146527753599</v>
+        <v>4185.152846282133</v>
       </c>
       <c r="E28">
-        <v>1140.928</v>
+        <v>1185.306</v>
       </c>
       <c r="F28">
-        <v>1153.828</v>
+        <v>1198.206</v>
       </c>
       <c r="G28">
         <v>482.1</v>
@@ -3589,28 +3589,28 @@
         <v>457.3</v>
       </c>
       <c r="M28">
-        <v>62.65286039999999</v>
+        <v>65.06258579999999</v>
       </c>
       <c r="N28">
-        <v>394.6471396</v>
+        <v>392.2374142</v>
       </c>
       <c r="O28">
-        <v>74.982956524</v>
+        <v>74.525108698</v>
       </c>
       <c r="P28">
-        <v>319.664183076</v>
+        <v>317.712305502</v>
       </c>
       <c r="Q28">
-        <v>422.1641830759999</v>
+        <v>420.2123055019999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1131573275727795</v>
+        <v>0.1139435568228559</v>
       </c>
       <c r="T28">
-        <v>1.135741309869371</v>
+        <v>1.148998264539589</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.298948477059478</v>
+        <v>7.028617051983201</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09505420648068483</v>
+        <v>0.0949364105575128</v>
       </c>
       <c r="C29">
-        <v>3469.046846282134</v>
+        <v>3433.714094997495</v>
       </c>
       <c r="D29">
-        <v>4185.152846282133</v>
+        <v>4194.198094997494</v>
       </c>
       <c r="E29">
-        <v>1185.306</v>
+        <v>1229.684</v>
       </c>
       <c r="F29">
-        <v>1198.206</v>
+        <v>1242.584</v>
       </c>
       <c r="G29">
         <v>482.1</v>
@@ -3671,28 +3671,28 @@
         <v>457.3</v>
       </c>
       <c r="M29">
-        <v>65.06258579999999</v>
+        <v>67.47231119999999</v>
       </c>
       <c r="N29">
-        <v>392.2374142</v>
+        <v>389.8276888</v>
       </c>
       <c r="O29">
-        <v>74.525108698</v>
+        <v>74.06726087200001</v>
       </c>
       <c r="P29">
-        <v>317.712305502</v>
+        <v>315.760427928</v>
       </c>
       <c r="Q29">
-        <v>420.2123055019999</v>
+        <v>418.260427928</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1139435568228559</v>
+        <v>0.1147516257743233</v>
       </c>
       <c r="T29">
-        <v>1.148998264539589</v>
+        <v>1.162623467950647</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.028617051983201</v>
+        <v>6.777595014412372</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0949364105575128</v>
+        <v>0.0948186146343408</v>
       </c>
       <c r="C30">
-        <v>3433.714094997495</v>
+        <v>3398.420526862431</v>
       </c>
       <c r="D30">
-        <v>4194.198094997494</v>
+        <v>4203.28252686243</v>
       </c>
       <c r="E30">
-        <v>1229.684</v>
+        <v>1274.062</v>
       </c>
       <c r="F30">
-        <v>1242.584</v>
+        <v>1286.962</v>
       </c>
       <c r="G30">
         <v>482.1</v>
@@ -3753,28 +3753,28 @@
         <v>457.3</v>
       </c>
       <c r="M30">
-        <v>67.47231119999999</v>
+        <v>69.88203660000001</v>
       </c>
       <c r="N30">
-        <v>389.8276888</v>
+        <v>387.4179634</v>
       </c>
       <c r="O30">
-        <v>74.06726087200001</v>
+        <v>73.609413046</v>
       </c>
       <c r="P30">
-        <v>315.760427928</v>
+        <v>313.808550354</v>
       </c>
       <c r="Q30">
-        <v>418.260427928</v>
+        <v>416.308550354</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1147516257743233</v>
+        <v>0.1155824572314659</v>
       </c>
       <c r="T30">
-        <v>1.162623467950647</v>
+        <v>1.176632479908495</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.777595014412372</v>
+        <v>6.543884841501599</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09481861463434077</v>
+        <v>0.09470081871116873</v>
       </c>
       <c r="C31">
-        <v>3398.420526862433</v>
+        <v>3363.166397036078</v>
       </c>
       <c r="D31">
-        <v>4203.282526862432</v>
+        <v>4212.406397036078</v>
       </c>
       <c r="E31">
-        <v>1274.062</v>
+        <v>1318.44</v>
       </c>
       <c r="F31">
-        <v>1286.962</v>
+        <v>1331.34</v>
       </c>
       <c r="G31">
         <v>482.1</v>
@@ -3835,28 +3835,28 @@
         <v>457.3</v>
       </c>
       <c r="M31">
-        <v>69.88203659999999</v>
+        <v>72.29176199999999</v>
       </c>
       <c r="N31">
-        <v>387.4179634</v>
+        <v>385.008238</v>
       </c>
       <c r="O31">
-        <v>73.609413046</v>
+        <v>73.15156522000001</v>
       </c>
       <c r="P31">
-        <v>313.808550354</v>
+        <v>311.85667278</v>
       </c>
       <c r="Q31">
-        <v>416.308550354</v>
+        <v>414.3566727799999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1155824572314659</v>
+        <v>0.1164370267302411</v>
       </c>
       <c r="T31">
-        <v>1.176632479908495</v>
+        <v>1.191041749350853</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.543884841501601</v>
+        <v>6.325755346784881</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09470081871116873</v>
+        <v>0.09458302278799671</v>
       </c>
       <c r="C32">
-        <v>3363.166397036078</v>
+        <v>3327.951962897824</v>
       </c>
       <c r="D32">
-        <v>4212.406397036078</v>
+        <v>4221.569962897824</v>
       </c>
       <c r="E32">
-        <v>1318.44</v>
+        <v>1362.818</v>
       </c>
       <c r="F32">
-        <v>1331.34</v>
+        <v>1375.718</v>
       </c>
       <c r="G32">
         <v>482.1</v>
@@ -3917,28 +3917,28 @@
         <v>457.3</v>
       </c>
       <c r="M32">
-        <v>72.29176199999999</v>
+        <v>74.70148739999999</v>
       </c>
       <c r="N32">
-        <v>385.008238</v>
+        <v>382.5985126</v>
       </c>
       <c r="O32">
-        <v>73.15156522000001</v>
+        <v>72.693717394</v>
       </c>
       <c r="P32">
-        <v>311.85667278</v>
+        <v>309.904795206</v>
       </c>
       <c r="Q32">
-        <v>414.3566727799999</v>
+        <v>412.404795206</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1164370267302411</v>
+        <v>0.1173163663594155</v>
       </c>
       <c r="T32">
-        <v>1.191041749350853</v>
+        <v>1.205868678777047</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.325755346784881</v>
+        <v>6.121698722695046</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09458302278799671</v>
+        <v>0.09472442686482468</v>
       </c>
       <c r="C33">
-        <v>3327.951962897824</v>
+        <v>3272.578657793067</v>
       </c>
       <c r="D33">
-        <v>4221.569962897824</v>
+        <v>4210.574657793066</v>
       </c>
       <c r="E33">
-        <v>1362.818</v>
+        <v>1407.196</v>
       </c>
       <c r="F33">
-        <v>1375.718</v>
+        <v>1420.096</v>
       </c>
       <c r="G33">
         <v>482.1</v>
@@ -3999,45 +3999,45 @@
         <v>457.3</v>
       </c>
       <c r="M33">
-        <v>74.70148739999999</v>
+        <v>78.53130879999999</v>
       </c>
       <c r="N33">
-        <v>382.5985126</v>
+        <v>378.7686912</v>
       </c>
       <c r="O33">
-        <v>72.693717394</v>
+        <v>71.96605132800001</v>
       </c>
       <c r="P33">
-        <v>309.904795206</v>
+        <v>306.802639872</v>
       </c>
       <c r="Q33">
-        <v>412.404795206</v>
+        <v>409.302639872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1173163663594155</v>
+        <v>0.1182215689188598</v>
       </c>
       <c r="T33">
-        <v>1.205868678777047</v>
+        <v>1.221131694362836</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.19</v>
       </c>
       <c r="W33">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.121698722695046</v>
+        <v>5.823155210167593</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09472442686482468</v>
+        <v>0.09461473094165267</v>
       </c>
       <c r="C34">
-        <v>3272.578657793067</v>
+        <v>3236.725406946146</v>
       </c>
       <c r="D34">
-        <v>4210.574657793066</v>
+        <v>4219.099406946146</v>
       </c>
       <c r="E34">
-        <v>1407.196</v>
+        <v>1451.574</v>
       </c>
       <c r="F34">
-        <v>1420.096</v>
+        <v>1464.474</v>
       </c>
       <c r="G34">
         <v>482.1</v>
@@ -4081,28 +4081,28 @@
         <v>457.3</v>
       </c>
       <c r="M34">
-        <v>78.53130879999999</v>
+        <v>80.9854122</v>
       </c>
       <c r="N34">
-        <v>378.7686912</v>
+        <v>376.3145878</v>
       </c>
       <c r="O34">
-        <v>71.96605132800001</v>
+        <v>71.499771682</v>
       </c>
       <c r="P34">
-        <v>306.802639872</v>
+        <v>304.814816118</v>
       </c>
       <c r="Q34">
-        <v>409.302639872</v>
+        <v>407.314816118</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1182215689188598</v>
+        <v>0.1191537924502279</v>
       </c>
       <c r="T34">
-        <v>1.221131694362836</v>
+        <v>1.23685032235417</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.823155210167593</v>
+        <v>5.646695961374634</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09461473094165267</v>
+        <v>0.09450503501848063</v>
       </c>
       <c r="C35">
-        <v>3236.725406946146</v>
+        <v>3200.906744621356</v>
       </c>
       <c r="D35">
-        <v>4219.099406946146</v>
+        <v>4227.658744621355</v>
       </c>
       <c r="E35">
-        <v>1451.574</v>
+        <v>1495.952</v>
       </c>
       <c r="F35">
-        <v>1464.474</v>
+        <v>1508.852</v>
       </c>
       <c r="G35">
         <v>482.1</v>
@@ -4163,28 +4163,28 @@
         <v>457.3</v>
       </c>
       <c r="M35">
-        <v>80.9854122</v>
+        <v>83.43951559999999</v>
       </c>
       <c r="N35">
-        <v>376.3145878</v>
+        <v>373.8604844</v>
       </c>
       <c r="O35">
-        <v>71.499771682</v>
+        <v>71.033492036</v>
       </c>
       <c r="P35">
-        <v>304.814816118</v>
+        <v>302.826992364</v>
       </c>
       <c r="Q35">
-        <v>407.314816118</v>
+        <v>405.326992364</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1191537924502279</v>
+        <v>0.1201142651795161</v>
       </c>
       <c r="T35">
-        <v>1.23685032235417</v>
+        <v>1.253045272405848</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.646695961374634</v>
+        <v>5.480616668393028</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09450503501848063</v>
+        <v>0.09439533909530862</v>
       </c>
       <c r="C36">
-        <v>3200.906744621356</v>
+        <v>3165.122881757076</v>
       </c>
       <c r="D36">
-        <v>4227.658744621355</v>
+        <v>4236.252881757076</v>
       </c>
       <c r="E36">
-        <v>1495.952</v>
+        <v>1540.33</v>
       </c>
       <c r="F36">
-        <v>1508.852</v>
+        <v>1553.23</v>
       </c>
       <c r="G36">
         <v>482.1</v>
@@ -4245,28 +4245,28 @@
         <v>457.3</v>
       </c>
       <c r="M36">
-        <v>83.43951559999999</v>
+        <v>85.89361899999999</v>
       </c>
       <c r="N36">
-        <v>373.8604844</v>
+        <v>371.406381</v>
       </c>
       <c r="O36">
-        <v>71.033492036</v>
+        <v>70.56721239000001</v>
       </c>
       <c r="P36">
-        <v>302.826992364</v>
+        <v>300.83916861</v>
       </c>
       <c r="Q36">
-        <v>405.326992364</v>
+        <v>403.3391686099999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1201142651795161</v>
+        <v>0.1211042909158594</v>
       </c>
       <c r="T36">
-        <v>1.253045272405848</v>
+        <v>1.269738528612962</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.480616668393028</v>
+        <v>5.324027620724656</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09439533909530862</v>
+        <v>0.09428564317213659</v>
       </c>
       <c r="C37">
-        <v>3165.122881757076</v>
+        <v>3129.374031010401</v>
       </c>
       <c r="D37">
-        <v>4236.252881757076</v>
+        <v>4244.882031010401</v>
       </c>
       <c r="E37">
-        <v>1540.33</v>
+        <v>1584.708</v>
       </c>
       <c r="F37">
-        <v>1553.23</v>
+        <v>1597.608</v>
       </c>
       <c r="G37">
         <v>482.1</v>
@@ -4327,28 +4327,28 @@
         <v>457.3</v>
       </c>
       <c r="M37">
-        <v>85.89361899999999</v>
+        <v>88.34772239999999</v>
       </c>
       <c r="N37">
-        <v>371.406381</v>
+        <v>368.9522776</v>
       </c>
       <c r="O37">
-        <v>70.56721239000001</v>
+        <v>70.100932744</v>
       </c>
       <c r="P37">
-        <v>300.83916861</v>
+        <v>298.851344856</v>
       </c>
       <c r="Q37">
-        <v>403.3391686099999</v>
+        <v>401.3513448559999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1211042909158594</v>
+        <v>0.1221252549564634</v>
       </c>
       <c r="T37">
-        <v>1.269738528612962</v>
+        <v>1.286953449076548</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.324027620724656</v>
+        <v>5.176137964593415</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09428564317213659</v>
+        <v>0.09417594724896458</v>
       </c>
       <c r="C38">
-        <v>3129.374031010402</v>
+        <v>3093.660406774668</v>
       </c>
       <c r="D38">
-        <v>4244.882031010401</v>
+        <v>4253.546406774667</v>
       </c>
       <c r="E38">
-        <v>1584.708</v>
+        <v>1629.086</v>
       </c>
       <c r="F38">
-        <v>1597.608</v>
+        <v>1641.986</v>
       </c>
       <c r="G38">
         <v>482.1</v>
@@ -4409,28 +4409,28 @@
         <v>457.3</v>
       </c>
       <c r="M38">
-        <v>88.34772239999998</v>
+        <v>90.80182579999999</v>
       </c>
       <c r="N38">
-        <v>368.9522776</v>
+        <v>366.4981742</v>
       </c>
       <c r="O38">
-        <v>70.100932744</v>
+        <v>69.634653098</v>
       </c>
       <c r="P38">
-        <v>298.851344856</v>
+        <v>296.863521102</v>
       </c>
       <c r="Q38">
-        <v>401.3513448559999</v>
+        <v>399.3635211019999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1221252549564634</v>
+        <v>0.123178630553912</v>
       </c>
       <c r="T38">
-        <v>1.286953449076548</v>
+        <v>1.304714874951677</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.176137964593416</v>
+        <v>5.036242343928728</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09417594724896458</v>
+        <v>0.09406625132579255</v>
       </c>
       <c r="C39">
-        <v>3093.660406774668</v>
+        <v>3057.982225197217</v>
       </c>
       <c r="D39">
-        <v>4253.546406774667</v>
+        <v>4262.246225197217</v>
       </c>
       <c r="E39">
-        <v>1629.086</v>
+        <v>1673.464</v>
       </c>
       <c r="F39">
-        <v>1641.986</v>
+        <v>1686.364</v>
       </c>
       <c r="G39">
         <v>482.1</v>
@@ -4491,28 +4491,28 @@
         <v>457.3</v>
       </c>
       <c r="M39">
-        <v>90.80182579999999</v>
+        <v>93.2559292</v>
       </c>
       <c r="N39">
-        <v>366.4981742</v>
+        <v>364.0440708</v>
       </c>
       <c r="O39">
-        <v>69.634653098</v>
+        <v>69.168373452</v>
       </c>
       <c r="P39">
-        <v>296.863521102</v>
+        <v>294.875697348</v>
       </c>
       <c r="Q39">
-        <v>399.3635211019999</v>
+        <v>397.375697348</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.123178630553912</v>
+        <v>0.1242659860093428</v>
       </c>
       <c r="T39">
-        <v>1.304714874951677</v>
+        <v>1.323049250048584</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.036242343928728</v>
+        <v>4.903709650667445</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09406625132579255</v>
+        <v>0.09395655540262052</v>
       </c>
       <c r="C40">
-        <v>3057.982225197217</v>
+        <v>3022.33970419737</v>
       </c>
       <c r="D40">
-        <v>4262.246225197217</v>
+        <v>4270.981704197369</v>
       </c>
       <c r="E40">
-        <v>1673.464</v>
+        <v>1717.842</v>
       </c>
       <c r="F40">
-        <v>1686.364</v>
+        <v>1730.742</v>
       </c>
       <c r="G40">
         <v>482.1</v>
@@ -4573,28 +4573,28 @@
         <v>457.3</v>
       </c>
       <c r="M40">
-        <v>93.2559292</v>
+        <v>95.71003259999999</v>
       </c>
       <c r="N40">
-        <v>364.0440708</v>
+        <v>361.5899674</v>
       </c>
       <c r="O40">
-        <v>69.168373452</v>
+        <v>68.70209380600001</v>
       </c>
       <c r="P40">
-        <v>294.875697348</v>
+        <v>292.887873594</v>
       </c>
       <c r="Q40">
-        <v>397.375697348</v>
+        <v>395.387873594</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1242659860093428</v>
+        <v>0.1253889924633123</v>
       </c>
       <c r="T40">
-        <v>1.323049250048584</v>
+        <v>1.341984752197849</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.903709650667445</v>
+        <v>4.777973505778537</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09395655540262052</v>
+        <v>0.0938468594794485</v>
       </c>
       <c r="C41">
-        <v>3022.33970419737</v>
+        <v>2986.733063484614</v>
       </c>
       <c r="D41">
-        <v>4270.981704197369</v>
+        <v>4279.753063484613</v>
       </c>
       <c r="E41">
-        <v>1717.842</v>
+        <v>1762.22</v>
       </c>
       <c r="F41">
-        <v>1730.742</v>
+        <v>1775.12</v>
       </c>
       <c r="G41">
         <v>482.1</v>
@@ -4655,28 +4655,28 @@
         <v>457.3</v>
       </c>
       <c r="M41">
-        <v>95.71003259999999</v>
+        <v>98.164136</v>
       </c>
       <c r="N41">
-        <v>361.5899674</v>
+        <v>359.135864</v>
       </c>
       <c r="O41">
-        <v>68.70209380600001</v>
+        <v>68.23581416</v>
       </c>
       <c r="P41">
-        <v>292.887873594</v>
+        <v>290.90004984</v>
       </c>
       <c r="Q41">
-        <v>395.387873594</v>
+        <v>393.40004984</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1253889924633123</v>
+        <v>0.1265494324657475</v>
       </c>
       <c r="T41">
-        <v>1.341984752197849</v>
+        <v>1.361551437752089</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.777973505778537</v>
+        <v>4.658524168134074</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0938468594794485</v>
+        <v>0.09373716355627647</v>
       </c>
       <c r="C42">
-        <v>2986.733063484614</v>
+        <v>2951.162524577034</v>
       </c>
       <c r="D42">
-        <v>4279.753063484613</v>
+        <v>4288.560524577033</v>
       </c>
       <c r="E42">
-        <v>1762.22</v>
+        <v>1806.598</v>
       </c>
       <c r="F42">
-        <v>1775.12</v>
+        <v>1819.498</v>
       </c>
       <c r="G42">
         <v>482.1</v>
@@ -4737,28 +4737,28 @@
         <v>457.3</v>
       </c>
       <c r="M42">
-        <v>98.164136</v>
+        <v>100.6182394</v>
       </c>
       <c r="N42">
-        <v>359.135864</v>
+        <v>356.6817606</v>
       </c>
       <c r="O42">
-        <v>68.23581416</v>
+        <v>67.769534514</v>
       </c>
       <c r="P42">
-        <v>290.90004984</v>
+        <v>288.912226086</v>
       </c>
       <c r="Q42">
-        <v>393.40004984</v>
+        <v>391.412226086</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1265494324657475</v>
+        <v>0.1277492094174177</v>
       </c>
       <c r="T42">
-        <v>1.361551437752089</v>
+        <v>1.381781400782744</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.658524168134074</v>
+        <v>4.544901627447876</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09373716355627647</v>
+        <v>0.09447796763310445</v>
       </c>
       <c r="C43">
-        <v>2951.162524577034</v>
+        <v>2848.000099236581</v>
       </c>
       <c r="D43">
-        <v>4288.560524577033</v>
+        <v>4229.776099236581</v>
       </c>
       <c r="E43">
-        <v>1806.598</v>
+        <v>1850.976</v>
       </c>
       <c r="F43">
-        <v>1819.498</v>
+        <v>1863.876</v>
       </c>
       <c r="G43">
         <v>482.1</v>
@@ -4819,45 +4819,45 @@
         <v>457.3</v>
       </c>
       <c r="M43">
-        <v>100.6182394</v>
+        <v>107.7320328</v>
       </c>
       <c r="N43">
-        <v>356.6817606</v>
+        <v>349.5679672</v>
       </c>
       <c r="O43">
-        <v>67.769534514</v>
+        <v>66.41791376800001</v>
       </c>
       <c r="P43">
-        <v>288.912226086</v>
+        <v>283.150053432</v>
       </c>
       <c r="Q43">
-        <v>391.412226086</v>
+        <v>385.6500534319999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1277492094174177</v>
+        <v>0.1289903579881111</v>
       </c>
       <c r="T43">
-        <v>1.381781400782744</v>
+        <v>1.40270894874549</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.544901627447876</v>
+        <v>4.244791341206364</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09447796763310444</v>
+        <v>0.09438852170993242</v>
       </c>
       <c r="C44">
-        <v>2848.000099236584</v>
+        <v>2810.634143816674</v>
       </c>
       <c r="D44">
-        <v>4229.776099236583</v>
+        <v>4236.788143816673</v>
       </c>
       <c r="E44">
-        <v>1850.975999999999</v>
+        <v>1895.354</v>
       </c>
       <c r="F44">
-        <v>1863.876</v>
+        <v>1908.254</v>
       </c>
       <c r="G44">
         <v>482.1</v>
@@ -4901,28 +4901,28 @@
         <v>457.3</v>
       </c>
       <c r="M44">
-        <v>107.7320328</v>
+        <v>110.2970812</v>
       </c>
       <c r="N44">
-        <v>349.5679672</v>
+        <v>347.0029188</v>
       </c>
       <c r="O44">
-        <v>66.41791376800001</v>
+        <v>65.93055457200001</v>
       </c>
       <c r="P44">
-        <v>283.150053432</v>
+        <v>281.072364228</v>
       </c>
       <c r="Q44">
-        <v>385.6500534319999</v>
+        <v>383.572364228</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1289903579881111</v>
+        <v>0.1302750556314604</v>
       </c>
       <c r="T44">
-        <v>1.40270894874549</v>
+        <v>1.424370796636754</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.244791341206364</v>
+        <v>4.14607526350389</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09438852170993242</v>
+        <v>0.0942990757867604</v>
       </c>
       <c r="C45">
-        <v>2810.634143816674</v>
+        <v>2773.291475877931</v>
       </c>
       <c r="D45">
-        <v>4236.788143816673</v>
+        <v>4243.82347587793</v>
       </c>
       <c r="E45">
-        <v>1895.354</v>
+        <v>1939.732</v>
       </c>
       <c r="F45">
-        <v>1908.254</v>
+        <v>1952.632</v>
       </c>
       <c r="G45">
         <v>482.1</v>
@@ -4983,28 +4983,28 @@
         <v>457.3</v>
       </c>
       <c r="M45">
-        <v>110.2970812</v>
+        <v>112.8621296</v>
       </c>
       <c r="N45">
-        <v>347.0029188</v>
+        <v>344.4378704</v>
       </c>
       <c r="O45">
-        <v>65.93055457200001</v>
+        <v>65.44319537600001</v>
       </c>
       <c r="P45">
-        <v>281.072364228</v>
+        <v>278.994675024</v>
       </c>
       <c r="Q45">
-        <v>383.572364228</v>
+        <v>381.4946750239999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1302750556314604</v>
+        <v>0.1316056353335007</v>
       </c>
       <c r="T45">
-        <v>1.424370796636754</v>
+        <v>1.446806281952707</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.14607526350389</v>
+        <v>4.051846280242438</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0942990757867604</v>
+        <v>0.09548537986358836</v>
       </c>
       <c r="C46">
-        <v>2773.291475877931</v>
+        <v>2637.464295272445</v>
       </c>
       <c r="D46">
-        <v>4243.82347587793</v>
+        <v>4152.374295272444</v>
       </c>
       <c r="E46">
-        <v>1939.732</v>
+        <v>1984.11</v>
       </c>
       <c r="F46">
-        <v>1952.632</v>
+        <v>1997.01</v>
       </c>
       <c r="G46">
         <v>482.1</v>
@@ -5065,45 +5065,45 @@
         <v>457.3</v>
       </c>
       <c r="M46">
-        <v>112.8621296</v>
+        <v>122.416713</v>
       </c>
       <c r="N46">
-        <v>344.4378704</v>
+        <v>334.883287</v>
       </c>
       <c r="O46">
-        <v>65.44319537600001</v>
+        <v>63.62782453</v>
       </c>
       <c r="P46">
-        <v>278.994675024</v>
+        <v>271.25546247</v>
       </c>
       <c r="Q46">
-        <v>381.4946750239999</v>
+        <v>373.7554624699999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1316056353335007</v>
+        <v>0.1329845997519788</v>
       </c>
       <c r="T46">
-        <v>1.446806281952707</v>
+        <v>1.470057603098329</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.051846280242438</v>
+        <v>3.735601036763665</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09548537986358836</v>
+        <v>0.09542428394041633</v>
       </c>
       <c r="C47">
-        <v>2637.464295272445</v>
+        <v>2597.699656391588</v>
       </c>
       <c r="D47">
-        <v>4152.374295272444</v>
+        <v>4156.987656391588</v>
       </c>
       <c r="E47">
-        <v>1984.11</v>
+        <v>2028.488</v>
       </c>
       <c r="F47">
-        <v>1997.01</v>
+        <v>2041.388</v>
       </c>
       <c r="G47">
         <v>482.1</v>
@@ -5147,28 +5147,28 @@
         <v>457.3</v>
       </c>
       <c r="M47">
-        <v>122.416713</v>
+        <v>125.1370844</v>
       </c>
       <c r="N47">
-        <v>334.883287</v>
+        <v>332.1629156</v>
       </c>
       <c r="O47">
-        <v>63.62782453</v>
+        <v>63.110953964</v>
       </c>
       <c r="P47">
-        <v>271.25546247</v>
+        <v>269.051961636</v>
       </c>
       <c r="Q47">
-        <v>373.7554624699999</v>
+        <v>371.5519616359999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1329845997519788</v>
+        <v>0.1344146369266969</v>
       </c>
       <c r="T47">
-        <v>1.470057603098329</v>
+        <v>1.494170084286383</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.735601036763665</v>
+        <v>3.654392318573151</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09542428394041633</v>
+        <v>0.09536318801724432</v>
       </c>
       <c r="C48">
-        <v>2597.699656391588</v>
+        <v>2557.945279963728</v>
       </c>
       <c r="D48">
-        <v>4156.987656391588</v>
+        <v>4161.611279963728</v>
       </c>
       <c r="E48">
-        <v>2028.488</v>
+        <v>2072.866</v>
       </c>
       <c r="F48">
-        <v>2041.388</v>
+        <v>2085.766</v>
       </c>
       <c r="G48">
         <v>482.1</v>
@@ -5229,28 +5229,28 @@
         <v>457.3</v>
       </c>
       <c r="M48">
-        <v>125.1370844</v>
+        <v>127.8574558</v>
       </c>
       <c r="N48">
-        <v>332.1629156</v>
+        <v>329.4425442</v>
       </c>
       <c r="O48">
-        <v>63.110953964</v>
+        <v>62.59408339800001</v>
       </c>
       <c r="P48">
-        <v>269.051961636</v>
+        <v>266.848460802</v>
       </c>
       <c r="Q48">
-        <v>371.5519616359999</v>
+        <v>369.348460802</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1344146369266969</v>
+        <v>0.1358986377683855</v>
       </c>
       <c r="T48">
-        <v>1.494170084286383</v>
+        <v>1.519192470424929</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.654392318573151</v>
+        <v>3.576639290518403</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09536318801724432</v>
+        <v>0.09530209209407228</v>
       </c>
       <c r="C49">
-        <v>2557.945279963728</v>
+        <v>2518.201200270342</v>
       </c>
       <c r="D49">
-        <v>4161.611279963728</v>
+        <v>4166.245200270341</v>
       </c>
       <c r="E49">
-        <v>2072.866</v>
+        <v>2117.244</v>
       </c>
       <c r="F49">
-        <v>2085.766</v>
+        <v>2130.144</v>
       </c>
       <c r="G49">
         <v>482.1</v>
@@ -5311,28 +5311,28 @@
         <v>457.3</v>
       </c>
       <c r="M49">
-        <v>127.8574558</v>
+        <v>130.5778272</v>
       </c>
       <c r="N49">
-        <v>329.4425442</v>
+        <v>326.7221728000001</v>
       </c>
       <c r="O49">
-        <v>62.59408339800001</v>
+        <v>62.07721283200001</v>
       </c>
       <c r="P49">
-        <v>266.848460802</v>
+        <v>264.6449599680001</v>
       </c>
       <c r="Q49">
-        <v>369.348460802</v>
+        <v>367.144959968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1358986377683855</v>
+        <v>0.1374397155655236</v>
       </c>
       <c r="T49">
-        <v>1.519192470424929</v>
+        <v>1.545177256030343</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.576639290518403</v>
+        <v>3.502125971965937</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09530209209407228</v>
+        <v>0.09635231617090027</v>
       </c>
       <c r="C50">
-        <v>2518.201200270342</v>
+        <v>2395.576237771996</v>
       </c>
       <c r="D50">
-        <v>4166.245200270341</v>
+        <v>4087.998237771995</v>
       </c>
       <c r="E50">
-        <v>2117.244</v>
+        <v>2161.621999999999</v>
       </c>
       <c r="F50">
-        <v>2130.144</v>
+        <v>2174.521999999999</v>
       </c>
       <c r="G50">
         <v>482.1</v>
@@ -5393,45 +5393,45 @@
         <v>457.3</v>
       </c>
       <c r="M50">
-        <v>130.5778272</v>
+        <v>139.3868602</v>
       </c>
       <c r="N50">
-        <v>326.7221728000001</v>
+        <v>317.9131398000001</v>
       </c>
       <c r="O50">
-        <v>62.07721283200001</v>
+        <v>60.40349656200002</v>
       </c>
       <c r="P50">
-        <v>264.6449599680001</v>
+        <v>257.5096432380001</v>
       </c>
       <c r="Q50">
-        <v>367.144959968</v>
+        <v>360.009643238</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1374397155655236</v>
+        <v>0.1390412277860789</v>
       </c>
       <c r="T50">
-        <v>1.545177256030342</v>
+        <v>1.572181052835968</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.19</v>
       </c>
       <c r="W50">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.502125971965937</v>
+        <v>3.280797051772604</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09635231617090027</v>
+        <v>0.09631390024772823</v>
       </c>
       <c r="C51">
-        <v>2395.576237771996</v>
+        <v>2354.008592393559</v>
       </c>
       <c r="D51">
-        <v>4087.998237771995</v>
+        <v>4090.808592393558</v>
       </c>
       <c r="E51">
-        <v>2161.621999999999</v>
+        <v>2206</v>
       </c>
       <c r="F51">
-        <v>2174.521999999999</v>
+        <v>2218.9</v>
       </c>
       <c r="G51">
         <v>482.1</v>
@@ -5475,28 +5475,28 @@
         <v>457.3</v>
       </c>
       <c r="M51">
-        <v>139.3868602</v>
+        <v>142.23149</v>
       </c>
       <c r="N51">
-        <v>317.9131398000001</v>
+        <v>315.0685100000001</v>
       </c>
       <c r="O51">
-        <v>60.40349656200002</v>
+        <v>59.86301690000001</v>
       </c>
       <c r="P51">
-        <v>257.5096432380001</v>
+        <v>255.2054931</v>
       </c>
       <c r="Q51">
-        <v>360.009643238</v>
+        <v>357.7054931</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1390412277860789</v>
+        <v>0.1407068004954564</v>
       </c>
       <c r="T51">
-        <v>1.572181052835968</v>
+        <v>1.600265001513818</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.280797051772604</v>
+        <v>3.215181110737152</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09631390024772823</v>
+        <v>0.09627548432455621</v>
       </c>
       <c r="C52">
-        <v>2354.008592393559</v>
+        <v>2312.444813712723</v>
       </c>
       <c r="D52">
-        <v>4090.808592393558</v>
+        <v>4093.622813712723</v>
       </c>
       <c r="E52">
-        <v>2206</v>
+        <v>2250.378</v>
       </c>
       <c r="F52">
-        <v>2218.9</v>
+        <v>2263.278</v>
       </c>
       <c r="G52">
         <v>482.1</v>
@@ -5557,28 +5557,28 @@
         <v>457.3</v>
       </c>
       <c r="M52">
-        <v>142.23149</v>
+        <v>145.0761198</v>
       </c>
       <c r="N52">
-        <v>315.0685100000001</v>
+        <v>312.2238802000001</v>
       </c>
       <c r="O52">
-        <v>59.86301690000001</v>
+        <v>59.32253723800001</v>
       </c>
       <c r="P52">
-        <v>255.2054931</v>
+        <v>252.9013429620001</v>
       </c>
       <c r="Q52">
-        <v>357.7054931</v>
+        <v>355.401342962</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1407068004954564</v>
+        <v>0.1424403557644004</v>
       </c>
       <c r="T52">
-        <v>1.600265001513818</v>
+        <v>1.629495233811173</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.215181110737152</v>
+        <v>3.152138343859953</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09627548432455621</v>
+        <v>0.09623706840138418</v>
       </c>
       <c r="C53">
-        <v>2312.444813712723</v>
+        <v>2270.884909715126</v>
       </c>
       <c r="D53">
-        <v>4093.622813712723</v>
+        <v>4096.440909715126</v>
       </c>
       <c r="E53">
-        <v>2250.378</v>
+        <v>2294.755999999999</v>
       </c>
       <c r="F53">
-        <v>2263.278</v>
+        <v>2307.655999999999</v>
       </c>
       <c r="G53">
         <v>482.1</v>
@@ -5639,28 +5639,28 @@
         <v>457.3</v>
       </c>
       <c r="M53">
-        <v>145.0761198</v>
+        <v>147.9207496</v>
       </c>
       <c r="N53">
-        <v>312.2238802000001</v>
+        <v>309.3792504</v>
       </c>
       <c r="O53">
-        <v>59.32253723800001</v>
+        <v>58.78205757600001</v>
       </c>
       <c r="P53">
-        <v>252.9013429620001</v>
+        <v>250.597192824</v>
       </c>
       <c r="Q53">
-        <v>355.401342962</v>
+        <v>353.097192824</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1424403557644004</v>
+        <v>0.1442461425028837</v>
       </c>
       <c r="T53">
-        <v>1.629495233811173</v>
+        <v>1.659943392454251</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.152138343859953</v>
+        <v>3.091520298785723</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09623706840138418</v>
+        <v>0.09619865247821215</v>
       </c>
       <c r="C54">
-        <v>2270.884909715126</v>
+        <v>2229.328888408408</v>
       </c>
       <c r="D54">
-        <v>4096.440909715126</v>
+        <v>4099.262888408407</v>
       </c>
       <c r="E54">
-        <v>2294.755999999999</v>
+        <v>2339.134</v>
       </c>
       <c r="F54">
-        <v>2307.655999999999</v>
+        <v>2352.034</v>
       </c>
       <c r="G54">
         <v>482.1</v>
@@ -5721,28 +5721,28 @@
         <v>457.3</v>
       </c>
       <c r="M54">
-        <v>147.9207496</v>
+        <v>150.7653794</v>
       </c>
       <c r="N54">
-        <v>309.3792504</v>
+        <v>306.5346206</v>
       </c>
       <c r="O54">
-        <v>58.78205757600001</v>
+        <v>58.24157791400001</v>
       </c>
       <c r="P54">
-        <v>250.597192824</v>
+        <v>248.293042686</v>
       </c>
       <c r="Q54">
-        <v>353.097192824</v>
+        <v>350.793042686</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1442461425028837</v>
+        <v>0.1461287712302386</v>
       </c>
       <c r="T54">
-        <v>1.659943392454251</v>
+        <v>1.691687217422566</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.091520298785723</v>
+        <v>3.03318972711052</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09619865247821215</v>
+        <v>0.09957195655504011</v>
       </c>
       <c r="C55">
-        <v>2229.328888408408</v>
+        <v>1951.126391542642</v>
       </c>
       <c r="D55">
-        <v>4099.262888408407</v>
+        <v>3865.438391542642</v>
       </c>
       <c r="E55">
-        <v>2339.134</v>
+        <v>2383.512</v>
       </c>
       <c r="F55">
-        <v>2352.034</v>
+        <v>2396.412</v>
       </c>
       <c r="G55">
         <v>482.1</v>
@@ -5803,45 +5803,45 @@
         <v>457.3</v>
       </c>
       <c r="M55">
-        <v>150.7653794</v>
+        <v>172.3020228</v>
       </c>
       <c r="N55">
-        <v>306.5346206</v>
+        <v>284.9979772</v>
       </c>
       <c r="O55">
-        <v>58.24157791400001</v>
+        <v>54.14961566800001</v>
       </c>
       <c r="P55">
-        <v>248.293042686</v>
+        <v>230.848361532</v>
       </c>
       <c r="Q55">
-        <v>350.793042686</v>
+        <v>333.348361532</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1461287712302386</v>
+        <v>0.148093253380522</v>
       </c>
       <c r="T55">
-        <v>1.691687217422566</v>
+        <v>1.724811208693851</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.19</v>
       </c>
       <c r="W55">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.03318972711052</v>
+        <v>2.654060541882391</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09957195655504011</v>
+        <v>0.0995967206318681</v>
       </c>
       <c r="C56">
-        <v>1951.126391542642</v>
+        <v>1905.130431381268</v>
       </c>
       <c r="D56">
-        <v>3865.438391542642</v>
+        <v>3863.820431381268</v>
       </c>
       <c r="E56">
-        <v>2383.512</v>
+        <v>2427.89</v>
       </c>
       <c r="F56">
-        <v>2396.412</v>
+        <v>2440.79</v>
       </c>
       <c r="G56">
         <v>482.1</v>
@@ -5885,28 +5885,28 @@
         <v>457.3</v>
       </c>
       <c r="M56">
-        <v>172.3020228</v>
+        <v>175.492801</v>
       </c>
       <c r="N56">
-        <v>284.9979772</v>
+        <v>281.807199</v>
       </c>
       <c r="O56">
-        <v>54.14961566800001</v>
+        <v>53.54336780999999</v>
       </c>
       <c r="P56">
-        <v>230.848361532</v>
+        <v>228.26383119</v>
       </c>
       <c r="Q56">
-        <v>333.348361532</v>
+        <v>330.7638311899999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.148093253380522</v>
+        <v>0.1501450458485958</v>
       </c>
       <c r="T56">
-        <v>1.724811208693851</v>
+        <v>1.759407377354972</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.654060541882391</v>
+        <v>2.605804895666346</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0995967206318681</v>
+        <v>0.09962148470869608</v>
       </c>
       <c r="C57">
-        <v>1905.130431381268</v>
+        <v>1859.135825115389</v>
       </c>
       <c r="D57">
-        <v>3863.820431381268</v>
+        <v>3862.203825115388</v>
       </c>
       <c r="E57">
-        <v>2427.89</v>
+        <v>2472.268</v>
       </c>
       <c r="F57">
-        <v>2440.79</v>
+        <v>2485.168</v>
       </c>
       <c r="G57">
         <v>482.1</v>
@@ -5967,28 +5967,28 @@
         <v>457.3</v>
       </c>
       <c r="M57">
-        <v>175.492801</v>
+        <v>178.6835792</v>
       </c>
       <c r="N57">
-        <v>281.807199</v>
+        <v>278.6164208</v>
       </c>
       <c r="O57">
-        <v>53.54336780999999</v>
+        <v>52.937119952</v>
       </c>
       <c r="P57">
-        <v>228.26383119</v>
+        <v>225.679300848</v>
       </c>
       <c r="Q57">
-        <v>330.7638311899999</v>
+        <v>328.179300848</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1501450458485958</v>
+        <v>0.1522901016106729</v>
       </c>
       <c r="T57">
-        <v>1.759407377354972</v>
+        <v>1.795576099137052</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.605804895666346</v>
+        <v>2.559272665386591</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09962148470869608</v>
+        <v>0.09964624878552404</v>
       </c>
       <c r="C58">
-        <v>1859.135825115389</v>
+        <v>1813.142571046321</v>
       </c>
       <c r="D58">
-        <v>3862.203825115388</v>
+        <v>3860.588571046321</v>
       </c>
       <c r="E58">
-        <v>2472.268</v>
+        <v>2516.646</v>
       </c>
       <c r="F58">
-        <v>2485.168</v>
+        <v>2529.546</v>
       </c>
       <c r="G58">
         <v>482.1</v>
@@ -6049,28 +6049,28 @@
         <v>457.3</v>
       </c>
       <c r="M58">
-        <v>178.6835792</v>
+        <v>181.8743574</v>
       </c>
       <c r="N58">
-        <v>278.6164208</v>
+        <v>275.4256426</v>
       </c>
       <c r="O58">
-        <v>52.937119952</v>
+        <v>52.330872094</v>
       </c>
       <c r="P58">
-        <v>225.679300848</v>
+        <v>223.094770506</v>
       </c>
       <c r="Q58">
-        <v>328.179300848</v>
+        <v>325.5947705059999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1522901016106729</v>
+        <v>0.1545349274081955</v>
       </c>
       <c r="T58">
-        <v>1.795576099137052</v>
+        <v>1.833427087048531</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.559272665386591</v>
+        <v>2.514373144941212</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09964624878552404</v>
+        <v>0.101503232862352</v>
       </c>
       <c r="C59">
-        <v>1813.142571046321</v>
+        <v>1651.373665552784</v>
       </c>
       <c r="D59">
-        <v>3860.588571046321</v>
+        <v>3743.197665552784</v>
       </c>
       <c r="E59">
-        <v>2516.646</v>
+        <v>2561.024</v>
       </c>
       <c r="F59">
-        <v>2529.546</v>
+        <v>2573.924</v>
       </c>
       <c r="G59">
         <v>482.1</v>
@@ -6131,45 +6131,45 @@
         <v>457.3</v>
       </c>
       <c r="M59">
-        <v>181.8743574</v>
+        <v>195.1034392</v>
       </c>
       <c r="N59">
-        <v>275.4256426</v>
+        <v>262.1965608</v>
       </c>
       <c r="O59">
-        <v>52.330872094</v>
+        <v>49.817346552</v>
       </c>
       <c r="P59">
-        <v>223.094770506</v>
+        <v>212.379214248</v>
       </c>
       <c r="Q59">
-        <v>325.5947705059999</v>
+        <v>314.8792142479999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1545349274081955</v>
+        <v>0.1568866496722667</v>
       </c>
       <c r="T59">
-        <v>1.833427087048531</v>
+        <v>1.873080502955796</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.19</v>
       </c>
       <c r="W59">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.514373144941212</v>
+        <v>2.343884873967921</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.101503232862352</v>
+        <v>0.10155958693918</v>
       </c>
       <c r="C60">
-        <v>1651.373665552784</v>
+        <v>1603.544702736978</v>
       </c>
       <c r="D60">
-        <v>3743.197665552784</v>
+        <v>3739.746702736977</v>
       </c>
       <c r="E60">
-        <v>2561.023999999999</v>
+        <v>2605.401999999999</v>
       </c>
       <c r="F60">
-        <v>2573.924</v>
+        <v>2618.301999999999</v>
       </c>
       <c r="G60">
         <v>482.1</v>
@@ -6213,28 +6213,28 @@
         <v>457.3</v>
       </c>
       <c r="M60">
-        <v>195.1034392</v>
+        <v>198.4672916</v>
       </c>
       <c r="N60">
-        <v>262.1965608</v>
+        <v>258.8327084000001</v>
       </c>
       <c r="O60">
-        <v>49.81734655200001</v>
+        <v>49.17821459600001</v>
       </c>
       <c r="P60">
-        <v>212.379214248</v>
+        <v>209.6544938040001</v>
       </c>
       <c r="Q60">
-        <v>314.879214248</v>
+        <v>312.154493804</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1568866496722667</v>
+        <v>0.159353090095561</v>
       </c>
       <c r="T60">
-        <v>1.873080502955795</v>
+        <v>1.914668231834145</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.343884873967922</v>
+        <v>2.304158011697279</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.10155958693918</v>
+        <v>0.101615941016008</v>
       </c>
       <c r="C61">
-        <v>1603.544702736978</v>
+        <v>1555.722097146275</v>
       </c>
       <c r="D61">
-        <v>3739.746702736977</v>
+        <v>3736.302097146274</v>
       </c>
       <c r="E61">
-        <v>2605.401999999999</v>
+        <v>2649.779999999999</v>
       </c>
       <c r="F61">
-        <v>2618.301999999999</v>
+        <v>2662.679999999999</v>
       </c>
       <c r="G61">
         <v>482.1</v>
@@ -6295,28 +6295,28 @@
         <v>457.3</v>
       </c>
       <c r="M61">
-        <v>198.4672916</v>
+        <v>201.831144</v>
       </c>
       <c r="N61">
-        <v>258.8327084000001</v>
+        <v>255.468856</v>
       </c>
       <c r="O61">
-        <v>49.17821459600001</v>
+        <v>48.53908264000001</v>
       </c>
       <c r="P61">
-        <v>209.6544938040001</v>
+        <v>206.92977336</v>
       </c>
       <c r="Q61">
-        <v>312.154493804</v>
+        <v>309.42977336</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.159353090095561</v>
+        <v>0.1619428525400199</v>
       </c>
       <c r="T61">
-        <v>1.914668231834145</v>
+        <v>1.958335347156413</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.304158011697279</v>
+        <v>2.265755378168991</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.101615941016008</v>
+        <v>0.1016722950928359</v>
       </c>
       <c r="C62">
-        <v>1555.722097146275</v>
+        <v>1507.905831230302</v>
       </c>
       <c r="D62">
-        <v>3736.302097146274</v>
+        <v>3732.863831230301</v>
       </c>
       <c r="E62">
-        <v>2649.779999999999</v>
+        <v>2694.157999999999</v>
       </c>
       <c r="F62">
-        <v>2662.679999999999</v>
+        <v>2707.058</v>
       </c>
       <c r="G62">
         <v>482.1</v>
@@ -6377,28 +6377,28 @@
         <v>457.3</v>
       </c>
       <c r="M62">
-        <v>201.831144</v>
+        <v>205.1949964</v>
       </c>
       <c r="N62">
-        <v>255.468856</v>
+        <v>252.1050036</v>
       </c>
       <c r="O62">
-        <v>48.53908264000001</v>
+        <v>47.899950684</v>
       </c>
       <c r="P62">
-        <v>206.92977336</v>
+        <v>204.205052916</v>
       </c>
       <c r="Q62">
-        <v>309.42977336</v>
+        <v>306.705052916</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1619428525400199</v>
+        <v>0.1646654233149639</v>
       </c>
       <c r="T62">
-        <v>1.958335347156413</v>
+        <v>2.004241801725977</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.265755378168991</v>
+        <v>2.228611847379335</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1016722950928359</v>
+        <v>0.1017286491696639</v>
       </c>
       <c r="C63">
-        <v>1507.905831230302</v>
+        <v>1460.095887503231</v>
       </c>
       <c r="D63">
-        <v>3732.863831230301</v>
+        <v>3729.43188750323</v>
       </c>
       <c r="E63">
-        <v>2694.157999999999</v>
+        <v>2738.536</v>
       </c>
       <c r="F63">
-        <v>2707.058</v>
+        <v>2751.436</v>
       </c>
       <c r="G63">
         <v>482.1</v>
@@ -6459,28 +6459,28 @@
         <v>457.3</v>
       </c>
       <c r="M63">
-        <v>205.1949964</v>
+        <v>208.5588488</v>
       </c>
       <c r="N63">
-        <v>252.1050036</v>
+        <v>248.7411512</v>
       </c>
       <c r="O63">
-        <v>47.899950684</v>
+        <v>47.260818728</v>
       </c>
       <c r="P63">
-        <v>204.205052916</v>
+        <v>201.480332472</v>
       </c>
       <c r="Q63">
-        <v>306.705052916</v>
+        <v>303.980332472</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1646654233149639</v>
+        <v>0.1675312872885892</v>
       </c>
       <c r="T63">
-        <v>2.004241801725977</v>
+        <v>2.052564385483412</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.228611847379335</v>
+        <v>2.192666495002249</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1017286491696639</v>
+        <v>0.1017850032464919</v>
       </c>
       <c r="C64">
-        <v>1460.095887503231</v>
+        <v>1412.292248543477</v>
       </c>
       <c r="D64">
-        <v>3729.43188750323</v>
+        <v>3726.006248543477</v>
       </c>
       <c r="E64">
-        <v>2738.536</v>
+        <v>2782.913999999999</v>
       </c>
       <c r="F64">
-        <v>2751.436</v>
+        <v>2795.813999999999</v>
       </c>
       <c r="G64">
         <v>482.1</v>
@@ -6541,28 +6541,28 @@
         <v>457.3</v>
       </c>
       <c r="M64">
-        <v>208.5588488</v>
+        <v>211.9227012</v>
       </c>
       <c r="N64">
-        <v>248.7411512</v>
+        <v>245.3772988</v>
       </c>
       <c r="O64">
-        <v>47.260818728</v>
+        <v>46.621686772</v>
       </c>
       <c r="P64">
-        <v>201.480332472</v>
+        <v>198.755612028</v>
       </c>
       <c r="Q64">
-        <v>303.980332472</v>
+        <v>301.255612028</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1675312872885892</v>
+        <v>0.1705520628283564</v>
       </c>
       <c r="T64">
-        <v>2.052564385483412</v>
+        <v>2.103499000795303</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.192666495002249</v>
+        <v>2.157862264922849</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1017850032464919</v>
+        <v>0.1018413573233199</v>
       </c>
       <c r="C65">
-        <v>1412.292248543477</v>
+        <v>1364.49489699341</v>
       </c>
       <c r="D65">
-        <v>3726.006248543477</v>
+        <v>3722.586896993409</v>
       </c>
       <c r="E65">
-        <v>2782.913999999999</v>
+        <v>2827.291999999999</v>
       </c>
       <c r="F65">
-        <v>2795.813999999999</v>
+        <v>2840.192</v>
       </c>
       <c r="G65">
         <v>482.1</v>
@@ -6623,28 +6623,28 @@
         <v>457.3</v>
       </c>
       <c r="M65">
-        <v>211.9227012</v>
+        <v>215.2865536</v>
       </c>
       <c r="N65">
-        <v>245.3772988</v>
+        <v>242.0134464</v>
       </c>
       <c r="O65">
-        <v>46.621686772</v>
+        <v>45.982554816</v>
       </c>
       <c r="P65">
-        <v>198.755612028</v>
+        <v>196.030891584</v>
       </c>
       <c r="Q65">
-        <v>301.255612028</v>
+        <v>298.530891584</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1705520628283564</v>
+        <v>0.1737406592314441</v>
       </c>
       <c r="T65">
-        <v>2.103499000795303</v>
+        <v>2.157263316957855</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.157862264922849</v>
+        <v>2.124145667033429</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1018413573233199</v>
+        <v>0.1018977114001478</v>
       </c>
       <c r="C66">
-        <v>1364.49489699341</v>
+        <v>1316.703815559052</v>
       </c>
       <c r="D66">
-        <v>3722.586896993409</v>
+        <v>3719.173815559051</v>
       </c>
       <c r="E66">
-        <v>2827.291999999999</v>
+        <v>2871.67</v>
       </c>
       <c r="F66">
-        <v>2840.192</v>
+        <v>2884.57</v>
       </c>
       <c r="G66">
         <v>482.1</v>
@@ -6705,28 +6705,28 @@
         <v>457.3</v>
       </c>
       <c r="M66">
-        <v>215.2865536</v>
+        <v>218.650406</v>
       </c>
       <c r="N66">
-        <v>242.0134464</v>
+        <v>238.649594</v>
       </c>
       <c r="O66">
-        <v>45.982554816</v>
+        <v>45.34342286</v>
       </c>
       <c r="P66">
-        <v>196.030891584</v>
+        <v>193.30617114</v>
       </c>
       <c r="Q66">
-        <v>298.530891584</v>
+        <v>295.8061711399999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1737406592314441</v>
+        <v>0.1771114611432796</v>
       </c>
       <c r="T66">
-        <v>2.157263316957855</v>
+        <v>2.214099879758267</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.124145667033429</v>
+        <v>2.091466502925222</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1018977114001478</v>
+        <v>0.1019540654769758</v>
       </c>
       <c r="C67">
-        <v>1316.703815559052</v>
+        <v>1268.918987009796</v>
       </c>
       <c r="D67">
-        <v>3719.173815559051</v>
+        <v>3715.766987009795</v>
       </c>
       <c r="E67">
-        <v>2871.67</v>
+        <v>2916.048</v>
       </c>
       <c r="F67">
-        <v>2884.57</v>
+        <v>2928.948</v>
       </c>
       <c r="G67">
         <v>482.1</v>
@@ -6787,28 +6787,28 @@
         <v>457.3</v>
       </c>
       <c r="M67">
-        <v>218.650406</v>
+        <v>222.0142584</v>
       </c>
       <c r="N67">
-        <v>238.649594</v>
+        <v>235.2857416</v>
       </c>
       <c r="O67">
-        <v>45.34342286</v>
+        <v>44.704290904</v>
       </c>
       <c r="P67">
-        <v>193.30617114</v>
+        <v>190.581450696</v>
       </c>
       <c r="Q67">
-        <v>295.8061711399999</v>
+        <v>293.0814506959999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1771114611432796</v>
+        <v>0.1806805455205171</v>
       </c>
       <c r="T67">
-        <v>2.214099879758267</v>
+        <v>2.274279769782232</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.091466502925222</v>
+        <v>2.059777616517264</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1019540654769758</v>
+        <v>0.1020104195538038</v>
       </c>
       <c r="C68">
-        <v>1268.918987009796</v>
+        <v>1221.14039417811</v>
       </c>
       <c r="D68">
-        <v>3715.766987009795</v>
+        <v>3712.366394178109</v>
       </c>
       <c r="E68">
-        <v>2916.048</v>
+        <v>2960.425999999999</v>
       </c>
       <c r="F68">
-        <v>2928.948</v>
+        <v>2973.326</v>
       </c>
       <c r="G68">
         <v>482.1</v>
@@ -6869,28 +6869,28 @@
         <v>457.3</v>
       </c>
       <c r="M68">
-        <v>222.0142584</v>
+        <v>225.3781108</v>
       </c>
       <c r="N68">
-        <v>235.2857416</v>
+        <v>231.9218892</v>
       </c>
       <c r="O68">
-        <v>44.704290904</v>
+        <v>44.06515894800001</v>
       </c>
       <c r="P68">
-        <v>190.581450696</v>
+        <v>187.856730252</v>
       </c>
       <c r="Q68">
-        <v>293.0814506959999</v>
+        <v>290.356730252</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1806805455205171</v>
+        <v>0.1844659380418297</v>
       </c>
       <c r="T68">
-        <v>2.274279769782232</v>
+        <v>2.338106925868257</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.059777616517264</v>
+        <v>2.029034667017007</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1020104195538038</v>
+        <v>0.1098881336306318</v>
       </c>
       <c r="C69">
-        <v>1221.14039417811</v>
+        <v>755.697782840261</v>
       </c>
       <c r="D69">
-        <v>3712.366394178109</v>
+        <v>3291.301782840261</v>
       </c>
       <c r="E69">
-        <v>2960.425999999999</v>
+        <v>3004.804</v>
       </c>
       <c r="F69">
-        <v>2973.326</v>
+        <v>3017.704</v>
       </c>
       <c r="G69">
         <v>482.1</v>
@@ -6951,45 +6951,45 @@
         <v>457.3</v>
       </c>
       <c r="M69">
-        <v>225.3781108</v>
+        <v>271.59336</v>
       </c>
       <c r="N69">
-        <v>231.9218892</v>
+        <v>185.70664</v>
       </c>
       <c r="O69">
-        <v>44.06515894800001</v>
+        <v>35.28426160000001</v>
       </c>
       <c r="P69">
-        <v>187.856730252</v>
+        <v>150.4223784</v>
       </c>
       <c r="Q69">
-        <v>290.356730252</v>
+        <v>252.9223784</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1844659380418297</v>
+        <v>0.1884879175957243</v>
       </c>
       <c r="T69">
-        <v>2.338106925868257</v>
+        <v>2.405923279209657</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.19</v>
       </c>
       <c r="W69">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.029034667017007</v>
+        <v>1.683767232011858</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1098881336306318</v>
+        <v>0.1100595077074597</v>
       </c>
       <c r="C70">
-        <v>755.697782840261</v>
+        <v>703.2187524246947</v>
       </c>
       <c r="D70">
-        <v>3291.301782840261</v>
+        <v>3283.200752424695</v>
       </c>
       <c r="E70">
-        <v>3004.804</v>
+        <v>3049.182</v>
       </c>
       <c r="F70">
-        <v>3017.704</v>
+        <v>3062.082</v>
       </c>
       <c r="G70">
         <v>482.1</v>
@@ -7033,28 +7033,28 @@
         <v>457.3</v>
       </c>
       <c r="M70">
-        <v>271.59336</v>
+        <v>275.58738</v>
       </c>
       <c r="N70">
-        <v>185.70664</v>
+        <v>181.71262</v>
       </c>
       <c r="O70">
-        <v>35.28426160000001</v>
+        <v>34.5253978</v>
       </c>
       <c r="P70">
-        <v>150.4223784</v>
+        <v>147.1872222</v>
       </c>
       <c r="Q70">
-        <v>252.9223784</v>
+        <v>249.6872222</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1884879175957243</v>
+        <v>0.1927693797014831</v>
       </c>
       <c r="T70">
-        <v>2.405923279209657</v>
+        <v>2.478114881153729</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.683767232011858</v>
+        <v>1.659364808359512</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1100595077074597</v>
+        <v>0.1102308817842877</v>
       </c>
       <c r="C71">
-        <v>703.2187524246947</v>
+        <v>650.779502961931</v>
       </c>
       <c r="D71">
-        <v>3283.200752424695</v>
+        <v>3275.139502961931</v>
       </c>
       <c r="E71">
-        <v>3049.182</v>
+        <v>3093.559999999999</v>
       </c>
       <c r="F71">
-        <v>3062.082</v>
+        <v>3106.46</v>
       </c>
       <c r="G71">
         <v>482.1</v>
@@ -7115,28 +7115,28 @@
         <v>457.3</v>
       </c>
       <c r="M71">
-        <v>275.58738</v>
+        <v>279.5814</v>
       </c>
       <c r="N71">
-        <v>181.71262</v>
+        <v>177.7186</v>
       </c>
       <c r="O71">
-        <v>34.5253978</v>
+        <v>33.76653400000001</v>
       </c>
       <c r="P71">
-        <v>147.1872222</v>
+        <v>143.952066</v>
       </c>
       <c r="Q71">
-        <v>249.6872222</v>
+        <v>246.452066</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1927693797014831</v>
+        <v>0.1973362726142924</v>
       </c>
       <c r="T71">
-        <v>2.478114881153729</v>
+        <v>2.555119256560738</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.659364808359512</v>
+        <v>1.635659596811519</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1102308817842877</v>
+        <v>0.1104022558611157</v>
       </c>
       <c r="C72">
-        <v>650.779502961931</v>
+        <v>598.3797421469035</v>
       </c>
       <c r="D72">
-        <v>3275.139502961931</v>
+        <v>3267.117742146903</v>
       </c>
       <c r="E72">
-        <v>3093.559999999999</v>
+        <v>3137.938</v>
       </c>
       <c r="F72">
-        <v>3106.46</v>
+        <v>3150.838</v>
       </c>
       <c r="G72">
         <v>482.1</v>
@@ -7197,28 +7197,28 @@
         <v>457.3</v>
       </c>
       <c r="M72">
-        <v>279.5814</v>
+        <v>283.57542</v>
       </c>
       <c r="N72">
-        <v>177.7186</v>
+        <v>173.7245800000001</v>
       </c>
       <c r="O72">
-        <v>33.76653400000001</v>
+        <v>33.00767020000001</v>
       </c>
       <c r="P72">
-        <v>143.952066</v>
+        <v>140.7169098000001</v>
       </c>
       <c r="Q72">
-        <v>246.452066</v>
+        <v>243.2169098</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1973362726142924</v>
+        <v>0.2022181236590196</v>
       </c>
       <c r="T72">
-        <v>2.555119256560738</v>
+        <v>2.637434278547542</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.635659596811519</v>
+        <v>1.612622137701498</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1104022558611157</v>
+        <v>0.1105736299379436</v>
       </c>
       <c r="C73">
-        <v>598.3797421469044</v>
+        <v>546.0191805313098</v>
       </c>
       <c r="D73">
-        <v>3267.117742146904</v>
+        <v>3259.135180531309</v>
       </c>
       <c r="E73">
-        <v>3137.937999999999</v>
+        <v>3182.315999999999</v>
       </c>
       <c r="F73">
-        <v>3150.837999999999</v>
+        <v>3195.215999999999</v>
       </c>
       <c r="G73">
         <v>482.1</v>
@@ -7279,28 +7279,28 @@
         <v>457.3</v>
       </c>
       <c r="M73">
-        <v>283.57542</v>
+        <v>287.5694399999999</v>
       </c>
       <c r="N73">
-        <v>173.7245800000001</v>
+        <v>169.7305600000001</v>
       </c>
       <c r="O73">
-        <v>33.00767020000001</v>
+        <v>32.24880640000001</v>
       </c>
       <c r="P73">
-        <v>140.7169098000001</v>
+        <v>137.4817536000001</v>
       </c>
       <c r="Q73">
-        <v>243.2169098</v>
+        <v>239.9817536</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2022181236590196</v>
+        <v>0.2074486783497987</v>
       </c>
       <c r="T73">
-        <v>2.637434278547541</v>
+        <v>2.725628944961973</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.612622137701498</v>
+        <v>1.590224608011199</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1105736299379436</v>
+        <v>0.1107450040147716</v>
       </c>
       <c r="C74">
-        <v>546.0191805313098</v>
+        <v>493.6975314887873</v>
       </c>
       <c r="D74">
-        <v>3259.135180531309</v>
+        <v>3251.191531488787</v>
       </c>
       <c r="E74">
-        <v>3182.315999999999</v>
+        <v>3226.694</v>
       </c>
       <c r="F74">
-        <v>3195.215999999999</v>
+        <v>3239.594</v>
       </c>
       <c r="G74">
         <v>482.1</v>
@@ -7361,28 +7361,28 @@
         <v>457.3</v>
       </c>
       <c r="M74">
-        <v>287.5694399999999</v>
+        <v>291.56346</v>
       </c>
       <c r="N74">
-        <v>169.7305600000001</v>
+        <v>165.73654</v>
       </c>
       <c r="O74">
-        <v>32.24880640000001</v>
+        <v>31.48994260000001</v>
       </c>
       <c r="P74">
-        <v>137.4817536000001</v>
+        <v>134.2465974</v>
       </c>
       <c r="Q74">
-        <v>239.9817536</v>
+        <v>236.7465974</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2074486783497987</v>
+        <v>0.2130666815361912</v>
       </c>
       <c r="T74">
-        <v>2.725628944961973</v>
+        <v>2.820356549629326</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.590224608011199</v>
+        <v>1.56844070927132</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1107450040147716</v>
+        <v>0.1109163780915996</v>
       </c>
       <c r="C75">
-        <v>493.6975314887873</v>
+        <v>441.4145111806206</v>
       </c>
       <c r="D75">
-        <v>3251.191531488787</v>
+        <v>3243.28651118062</v>
       </c>
       <c r="E75">
-        <v>3226.694</v>
+        <v>3271.071999999999</v>
       </c>
       <c r="F75">
-        <v>3239.594</v>
+        <v>3283.971999999999</v>
       </c>
       <c r="G75">
         <v>482.1</v>
@@ -7443,28 +7443,28 @@
         <v>457.3</v>
       </c>
       <c r="M75">
-        <v>291.56346</v>
+        <v>295.5574799999999</v>
       </c>
       <c r="N75">
-        <v>165.73654</v>
+        <v>161.7425200000001</v>
       </c>
       <c r="O75">
-        <v>31.48994260000001</v>
+        <v>30.73107880000001</v>
       </c>
       <c r="P75">
-        <v>134.2465974</v>
+        <v>131.0114412000001</v>
       </c>
       <c r="Q75">
-        <v>236.7465974</v>
+        <v>233.5114412</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2130666815361912</v>
+        <v>0.2191168388138446</v>
       </c>
       <c r="T75">
-        <v>2.820356549629326</v>
+        <v>2.922370893117245</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.56844070927132</v>
+        <v>1.547245564551437</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1109163780915996</v>
+        <v>0.1110877521684276</v>
       </c>
       <c r="C76">
-        <v>441.4145111806206</v>
+        <v>389.1698385219192</v>
       </c>
       <c r="D76">
-        <v>3243.28651118062</v>
+        <v>3235.419838521919</v>
       </c>
       <c r="E76">
-        <v>3271.071999999999</v>
+        <v>3315.449999999999</v>
       </c>
       <c r="F76">
-        <v>3283.971999999999</v>
+        <v>3328.349999999999</v>
       </c>
       <c r="G76">
         <v>482.1</v>
@@ -7525,28 +7525,28 @@
         <v>457.3</v>
       </c>
       <c r="M76">
-        <v>295.5574799999999</v>
+        <v>299.5514999999999</v>
       </c>
       <c r="N76">
-        <v>161.7425200000001</v>
+        <v>157.7485000000001</v>
       </c>
       <c r="O76">
-        <v>30.73107880000001</v>
+        <v>29.97221500000002</v>
       </c>
       <c r="P76">
-        <v>131.0114412000001</v>
+        <v>127.7762850000001</v>
       </c>
       <c r="Q76">
-        <v>233.5114412</v>
+        <v>230.276285</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2191168388138446</v>
+        <v>0.2256510086737103</v>
       </c>
       <c r="T76">
-        <v>2.922370893117245</v>
+        <v>3.032546384084197</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.547245564551437</v>
+        <v>1.526615623690752</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1110877521684276</v>
+        <v>0.1112591262452556</v>
       </c>
       <c r="C77">
-        <v>389.1698385219192</v>
+        <v>336.9632351483115</v>
       </c>
       <c r="D77">
-        <v>3235.419838521919</v>
+        <v>3227.591235148311</v>
       </c>
       <c r="E77">
-        <v>3315.449999999999</v>
+        <v>3359.828</v>
       </c>
       <c r="F77">
-        <v>3328.349999999999</v>
+        <v>3372.728</v>
       </c>
       <c r="G77">
         <v>482.1</v>
@@ -7607,28 +7607,28 @@
         <v>457.3</v>
       </c>
       <c r="M77">
-        <v>299.5514999999999</v>
+        <v>303.54552</v>
       </c>
       <c r="N77">
-        <v>157.7485000000001</v>
+        <v>153.7544800000001</v>
       </c>
       <c r="O77">
-        <v>29.97221500000002</v>
+        <v>29.21335120000001</v>
       </c>
       <c r="P77">
-        <v>127.7762850000001</v>
+        <v>124.5411288000001</v>
       </c>
       <c r="Q77">
-        <v>230.276285</v>
+        <v>227.0411288</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2256510086737103</v>
+        <v>0.2327296926885648</v>
       </c>
       <c r="T77">
-        <v>3.032546384084197</v>
+        <v>3.151903165965062</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.526615623690752</v>
+        <v>1.50652857601061</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1112591262452556</v>
+        <v>0.1494325893624449</v>
       </c>
       <c r="C78">
-        <v>336.9632351483115</v>
+        <v>-837.7741152295648</v>
       </c>
       <c r="D78">
-        <v>3227.591235148311</v>
+        <v>2097.231884770435</v>
       </c>
       <c r="E78">
-        <v>3359.828</v>
+        <v>3404.205999999999</v>
       </c>
       <c r="F78">
-        <v>3372.728</v>
+        <v>3417.105999999999</v>
       </c>
       <c r="G78">
         <v>482.1</v>
@@ -7689,45 +7689,45 @@
         <v>457.3</v>
       </c>
       <c r="M78">
-        <v>303.54552</v>
+        <v>501.6311607999999</v>
       </c>
       <c r="N78">
-        <v>153.7544800000001</v>
+        <v>-44.33116079999991</v>
       </c>
       <c r="O78">
-        <v>29.21335120000001</v>
+        <v>-8.422920551999983</v>
       </c>
       <c r="P78">
-        <v>124.5411288000001</v>
+        <v>-35.90824024799993</v>
       </c>
       <c r="Q78">
-        <v>227.0411288</v>
+        <v>66.59175975200002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2327296926885648</v>
+        <v>0.2433714553751252</v>
       </c>
       <c r="T78">
-        <v>3.151903165965062</v>
+        <v>3.331338573046703</v>
       </c>
       <c r="U78">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.19</v>
+        <v>0.1732089367443459</v>
       </c>
       <c r="W78">
-        <v>0.07290000000000001</v>
+        <v>0.12137292808593</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.50652857601061</v>
+        <v>0.9116259828649785</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1494325893624449</v>
+        <v>0.1504425893624449</v>
       </c>
       <c r="C79">
-        <v>-837.7741152295648</v>
+        <v>-901.4068958302328</v>
       </c>
       <c r="D79">
-        <v>2097.231884770435</v>
+        <v>2077.977104169767</v>
       </c>
       <c r="E79">
-        <v>3404.205999999999</v>
+        <v>3448.583999999999</v>
       </c>
       <c r="F79">
-        <v>3417.105999999999</v>
+        <v>3461.483999999999</v>
       </c>
       <c r="G79">
         <v>482.1</v>
@@ -7771,37 +7771,37 @@
         <v>457.3</v>
       </c>
       <c r="M79">
-        <v>501.6311607999999</v>
+        <v>508.1458512</v>
       </c>
       <c r="N79">
-        <v>-44.33116079999991</v>
+        <v>-50.84585119999997</v>
       </c>
       <c r="O79">
-        <v>-8.422920551999983</v>
+        <v>-9.660711727999994</v>
       </c>
       <c r="P79">
-        <v>-35.90824024799993</v>
+        <v>-41.18513947199997</v>
       </c>
       <c r="Q79">
-        <v>66.59175975200002</v>
+        <v>61.31486052799997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2433714553751252</v>
+        <v>0.2523519760739945</v>
       </c>
       <c r="T79">
-        <v>3.331338573046703</v>
+        <v>3.482763053639735</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1732089367443459</v>
+        <v>0.1709883093501876</v>
       </c>
       <c r="W79">
-        <v>0.12137292808593</v>
+        <v>0.1216989161873925</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9116259828649785</v>
+        <v>0.8999384702641453</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1504425893624449</v>
+        <v>0.1514525893624449</v>
       </c>
       <c r="C80">
-        <v>-901.4068958302328</v>
+        <v>-964.6893349125285</v>
       </c>
       <c r="D80">
-        <v>2077.977104169767</v>
+        <v>2059.072665087471</v>
       </c>
       <c r="E80">
-        <v>3448.583999999999</v>
+        <v>3492.962</v>
       </c>
       <c r="F80">
-        <v>3461.483999999999</v>
+        <v>3505.862</v>
       </c>
       <c r="G80">
         <v>482.1</v>
@@ -7853,37 +7853,37 @@
         <v>457.3</v>
       </c>
       <c r="M80">
-        <v>508.1458512</v>
+        <v>514.6605416</v>
       </c>
       <c r="N80">
-        <v>-50.84585119999997</v>
+        <v>-57.36054159999998</v>
       </c>
       <c r="O80">
-        <v>-9.660711727999994</v>
+        <v>-10.898502904</v>
       </c>
       <c r="P80">
-        <v>-41.18513947199997</v>
+        <v>-46.46203869599998</v>
       </c>
       <c r="Q80">
-        <v>61.31486052799997</v>
+        <v>56.03796130399996</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2523519760739945</v>
+        <v>0.2621877844584705</v>
       </c>
       <c r="T80">
-        <v>3.482763053639735</v>
+        <v>3.648608913336866</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1709883093501876</v>
+        <v>0.1688239003710713</v>
       </c>
       <c r="W80">
-        <v>0.1216989161873925</v>
+        <v>0.1220166514255267</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8999384702641453</v>
+        <v>0.8885468440582701</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1514525893624449</v>
+        <v>0.1524625893624449</v>
       </c>
       <c r="C81">
-        <v>-964.6893349125285</v>
+        <v>-1027.630907990098</v>
       </c>
       <c r="D81">
-        <v>2059.072665087471</v>
+        <v>2040.509092009902</v>
       </c>
       <c r="E81">
-        <v>3492.962</v>
+        <v>3537.34</v>
       </c>
       <c r="F81">
-        <v>3505.862</v>
+        <v>3550.24</v>
       </c>
       <c r="G81">
         <v>482.1</v>
@@ -7935,37 +7935,37 @@
         <v>457.3</v>
       </c>
       <c r="M81">
-        <v>514.6605416</v>
+        <v>521.1752320000001</v>
       </c>
       <c r="N81">
-        <v>-57.36054159999998</v>
+        <v>-63.87523200000004</v>
       </c>
       <c r="O81">
-        <v>-10.898502904</v>
+        <v>-12.13629408000001</v>
       </c>
       <c r="P81">
-        <v>-46.46203869599998</v>
+        <v>-51.73893792000003</v>
       </c>
       <c r="Q81">
-        <v>56.03796130399996</v>
+        <v>50.76106207999991</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2621877844584705</v>
+        <v>0.2730071736813939</v>
       </c>
       <c r="T81">
-        <v>3.648608913336866</v>
+        <v>3.831039359003708</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1688239003710713</v>
+        <v>0.1667136016164329</v>
       </c>
       <c r="W81">
-        <v>0.1220166514255267</v>
+        <v>0.1223264432827077</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8885468440582701</v>
+        <v>0.8774400085075416</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1524625893624449</v>
+        <v>0.1534725893624449</v>
       </c>
       <c r="C82">
-        <v>-1027.630907990098</v>
+        <v>-1090.240751923676</v>
       </c>
       <c r="D82">
-        <v>2040.509092009902</v>
+        <v>2022.277248076324</v>
       </c>
       <c r="E82">
-        <v>3537.34</v>
+        <v>3581.717999999999</v>
       </c>
       <c r="F82">
-        <v>3550.24</v>
+        <v>3594.617999999999</v>
       </c>
       <c r="G82">
         <v>482.1</v>
@@ -8017,37 +8017,37 @@
         <v>457.3</v>
       </c>
       <c r="M82">
-        <v>521.1752320000001</v>
+        <v>527.6899224</v>
       </c>
       <c r="N82">
-        <v>-63.87523200000004</v>
+        <v>-70.38992239999999</v>
       </c>
       <c r="O82">
-        <v>-12.13629408000001</v>
+        <v>-13.374085256</v>
       </c>
       <c r="P82">
-        <v>-51.73893792000003</v>
+        <v>-57.01583714399999</v>
       </c>
       <c r="Q82">
-        <v>50.76106207999991</v>
+        <v>45.48416285599995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2730071736813939</v>
+        <v>0.2849654459804147</v>
       </c>
       <c r="T82">
-        <v>3.831039359003708</v>
+        <v>4.032673009477588</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1667136016164329</v>
+        <v>0.1646554090038844</v>
       </c>
       <c r="W82">
-        <v>0.1223264432827077</v>
+        <v>0.1226285859582298</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8774400085075416</v>
+        <v>0.8666074158099177</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1534725893624449</v>
+        <v>0.1544825893624449</v>
       </c>
       <c r="C83">
-        <v>-1090.240751923676</v>
+        <v>-1152.527679916335</v>
       </c>
       <c r="D83">
-        <v>2022.277248076324</v>
+        <v>2004.368320083664</v>
       </c>
       <c r="E83">
-        <v>3581.717999999999</v>
+        <v>3626.096</v>
       </c>
       <c r="F83">
-        <v>3594.617999999999</v>
+        <v>3638.996</v>
       </c>
       <c r="G83">
         <v>482.1</v>
@@ -8099,37 +8099,37 @@
         <v>457.3</v>
       </c>
       <c r="M83">
-        <v>527.6899224</v>
+        <v>534.2046127999999</v>
       </c>
       <c r="N83">
-        <v>-70.38992239999999</v>
+        <v>-76.90461279999994</v>
       </c>
       <c r="O83">
-        <v>-13.374085256</v>
+        <v>-14.61187643199999</v>
       </c>
       <c r="P83">
-        <v>-57.01583714399999</v>
+        <v>-62.29273636799995</v>
       </c>
       <c r="Q83">
-        <v>45.48416285599995</v>
+        <v>40.20726363199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2849654459804147</v>
+        <v>0.2982524152015489</v>
       </c>
       <c r="T83">
-        <v>4.032673009477588</v>
+        <v>4.25671039889301</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1646554090038844</v>
+        <v>0.1626474162111541</v>
       </c>
       <c r="W83">
-        <v>0.1226285859582298</v>
+        <v>0.1229233593002026</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8666074158099177</v>
+        <v>0.8560390326902847</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1544825893624449</v>
+        <v>0.1554925893624449</v>
       </c>
       <c r="C84">
-        <v>-1152.527679916335</v>
+        <v>-1214.500195718962</v>
       </c>
       <c r="D84">
-        <v>2004.368320083664</v>
+        <v>1986.773804281037</v>
       </c>
       <c r="E84">
-        <v>3626.096</v>
+        <v>3670.474</v>
       </c>
       <c r="F84">
-        <v>3638.996</v>
+        <v>3683.374</v>
       </c>
       <c r="G84">
         <v>482.1</v>
@@ -8181,37 +8181,37 @@
         <v>457.3</v>
       </c>
       <c r="M84">
-        <v>534.2046127999999</v>
+        <v>540.7193032</v>
       </c>
       <c r="N84">
-        <v>-76.90461279999994</v>
+        <v>-83.4193032</v>
       </c>
       <c r="O84">
-        <v>-14.61187643199999</v>
+        <v>-15.849667608</v>
       </c>
       <c r="P84">
-        <v>-62.29273636799995</v>
+        <v>-67.569635592</v>
       </c>
       <c r="Q84">
-        <v>40.20726363199999</v>
+        <v>34.93036440799995</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2982524152015489</v>
+        <v>0.3131025572722283</v>
       </c>
       <c r="T84">
-        <v>4.25671039889301</v>
+        <v>4.507105128239658</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1626474162111541</v>
+        <v>0.1606878087869233</v>
       </c>
       <c r="W84">
-        <v>0.1229233593002026</v>
+        <v>0.1232110296700797</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8560390326902847</v>
+        <v>0.8457253094048595</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1554925893624449</v>
+        <v>0.1565025893624449</v>
       </c>
       <c r="C85">
-        <v>-1214.500195718962</v>
+        <v>-1276.166507094056</v>
       </c>
       <c r="D85">
-        <v>1986.773804281037</v>
+        <v>1969.485492905944</v>
       </c>
       <c r="E85">
-        <v>3670.474</v>
+        <v>3714.852</v>
       </c>
       <c r="F85">
-        <v>3683.374</v>
+        <v>3727.752</v>
       </c>
       <c r="G85">
         <v>482.1</v>
@@ -8263,37 +8263,37 @@
         <v>457.3</v>
       </c>
       <c r="M85">
-        <v>540.7193032</v>
+        <v>547.2339936000001</v>
       </c>
       <c r="N85">
-        <v>-83.4193032</v>
+        <v>-89.93399360000006</v>
       </c>
       <c r="O85">
-        <v>-15.849667608</v>
+        <v>-17.08745878400001</v>
       </c>
       <c r="P85">
-        <v>-67.569635592</v>
+        <v>-72.84653481600006</v>
       </c>
       <c r="Q85">
-        <v>34.93036440799995</v>
+        <v>29.65346518399988</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3131025572722283</v>
+        <v>0.3298089671017426</v>
       </c>
       <c r="T85">
-        <v>4.507105128239658</v>
+        <v>4.788799198754638</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1606878087869233</v>
+        <v>0.1587748586823171</v>
       </c>
       <c r="W85">
-        <v>0.1232110296700797</v>
+        <v>0.1234918507454359</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8457253094048595</v>
+        <v>0.8356571509595634</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1565025893624449</v>
+        <v>0.1575125893624449</v>
       </c>
       <c r="C86">
-        <v>-1276.166507094055</v>
+        <v>-1337.534538582644</v>
       </c>
       <c r="D86">
-        <v>1969.485492905944</v>
+        <v>1952.495461417355</v>
       </c>
       <c r="E86">
-        <v>3714.851999999999</v>
+        <v>3759.229999999999</v>
       </c>
       <c r="F86">
-        <v>3727.751999999999</v>
+        <v>3772.129999999999</v>
       </c>
       <c r="G86">
         <v>482.1</v>
@@ -8345,37 +8345,37 @@
         <v>457.3</v>
       </c>
       <c r="M86">
-        <v>547.2339936</v>
+        <v>553.7486839999999</v>
       </c>
       <c r="N86">
-        <v>-89.93399359999995</v>
+        <v>-96.4486839999999</v>
       </c>
       <c r="O86">
-        <v>-17.08745878399999</v>
+        <v>-18.32524995999998</v>
       </c>
       <c r="P86">
-        <v>-72.84653481599996</v>
+        <v>-78.12343403999992</v>
       </c>
       <c r="Q86">
-        <v>29.65346518399998</v>
+        <v>24.37656596000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3298089671017424</v>
+        <v>0.3487428982418586</v>
       </c>
       <c r="T86">
-        <v>4.788799198754634</v>
+        <v>5.10805247867161</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1587748586823171</v>
+        <v>0.1569069191684075</v>
       </c>
       <c r="W86">
-        <v>0.1234918507454359</v>
+        <v>0.1237660642660778</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8356571509595636</v>
+        <v>0.8258258903600394</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1575125893624449</v>
+        <v>0.1585225893624449</v>
       </c>
       <c r="C87">
-        <v>-1337.534538582644</v>
+        <v>-1398.611943616048</v>
       </c>
       <c r="D87">
-        <v>1952.495461417355</v>
+        <v>1935.796056383951</v>
       </c>
       <c r="E87">
-        <v>3759.229999999999</v>
+        <v>3803.607999999999</v>
       </c>
       <c r="F87">
-        <v>3772.129999999999</v>
+        <v>3816.507999999999</v>
       </c>
       <c r="G87">
         <v>482.1</v>
@@ -8427,37 +8427,37 @@
         <v>457.3</v>
       </c>
       <c r="M87">
-        <v>553.7486839999999</v>
+        <v>560.2633744</v>
       </c>
       <c r="N87">
-        <v>-96.4486839999999</v>
+        <v>-102.9633744</v>
       </c>
       <c r="O87">
-        <v>-18.32524995999998</v>
+        <v>-19.56304113599999</v>
       </c>
       <c r="P87">
-        <v>-78.12343403999992</v>
+        <v>-83.40033326399997</v>
       </c>
       <c r="Q87">
-        <v>24.37656596000002</v>
+        <v>19.09966673599997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3487428982418586</v>
+        <v>0.3703816766877056</v>
       </c>
       <c r="T87">
-        <v>5.10805247867161</v>
+        <v>5.472913370005297</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1569069191684075</v>
+        <v>0.1550824201083097</v>
       </c>
       <c r="W87">
-        <v>0.1237660642660778</v>
+        <v>0.1240339007281002</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8258258903600394</v>
+        <v>0.8162232637279458</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1585225893624449</v>
+        <v>0.1595325893624449</v>
       </c>
       <c r="C88">
-        <v>-1398.611943616048</v>
+        <v>-1459.406116011362</v>
       </c>
       <c r="D88">
-        <v>1935.796056383951</v>
+        <v>1919.379883988637</v>
       </c>
       <c r="E88">
-        <v>3803.607999999999</v>
+        <v>3847.985999999999</v>
       </c>
       <c r="F88">
-        <v>3816.507999999999</v>
+        <v>3860.886</v>
       </c>
       <c r="G88">
         <v>482.1</v>
@@ -8509,37 +8509,37 @@
         <v>457.3</v>
       </c>
       <c r="M88">
-        <v>560.2633744</v>
+        <v>566.7780648</v>
       </c>
       <c r="N88">
-        <v>-102.9633744</v>
+        <v>-109.4780648</v>
       </c>
       <c r="O88">
-        <v>-19.56304113599999</v>
+        <v>-20.800832312</v>
       </c>
       <c r="P88">
-        <v>-83.40033326399997</v>
+        <v>-88.67723248800002</v>
       </c>
       <c r="Q88">
-        <v>19.09966673599997</v>
+        <v>13.82276751199993</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3703816766877056</v>
+        <v>0.3953494979713753</v>
       </c>
       <c r="T88">
-        <v>5.472913370005297</v>
+        <v>5.89390670615955</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1550824201083097</v>
+        <v>0.1532998635553406</v>
       </c>
       <c r="W88">
-        <v>0.1240339007281002</v>
+        <v>0.124295580030076</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8162232637279458</v>
+        <v>0.8068413871333716</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1595325893624449</v>
+        <v>0.2099432473812833</v>
       </c>
       <c r="C89">
-        <v>-1459.406116011362</v>
+        <v>-2074.589664950026</v>
       </c>
       <c r="D89">
-        <v>1919.379883988637</v>
+        <v>1348.574335049973</v>
       </c>
       <c r="E89">
-        <v>3847.985999999999</v>
+        <v>3892.363999999999</v>
       </c>
       <c r="F89">
-        <v>3860.886</v>
+        <v>3905.263999999999</v>
       </c>
       <c r="G89">
         <v>482.1</v>
@@ -8591,45 +8591,45 @@
         <v>457.3</v>
       </c>
       <c r="M89">
-        <v>566.7780648</v>
+        <v>784.1770111999998</v>
       </c>
       <c r="N89">
-        <v>-109.4780648</v>
+        <v>-326.8770111999998</v>
       </c>
       <c r="O89">
-        <v>-20.800832312</v>
+        <v>-62.10663212799997</v>
       </c>
       <c r="P89">
-        <v>-88.67723248800002</v>
+        <v>-264.7703790719999</v>
       </c>
       <c r="Q89">
-        <v>13.82276751199993</v>
+        <v>-162.2703790719999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3953494979713753</v>
+        <v>0.4401507729593095</v>
       </c>
       <c r="T89">
-        <v>5.89390670615955</v>
+        <v>6.649320564935874</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1532998635553406</v>
+        <v>0.1108002386693787</v>
       </c>
       <c r="W89">
-        <v>0.124295580030076</v>
+        <v>0.1785513120751888</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8068413871333716</v>
+        <v>0.5831591508914666</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2099432473812833</v>
+        <v>0.2114932473812833</v>
       </c>
       <c r="C90">
-        <v>-2074.589664950026</v>
+        <v>-2131.187302485489</v>
       </c>
       <c r="D90">
-        <v>1348.574335049973</v>
+        <v>1336.35469751451</v>
       </c>
       <c r="E90">
-        <v>3892.363999999999</v>
+        <v>3936.741999999999</v>
       </c>
       <c r="F90">
-        <v>3905.263999999999</v>
+        <v>3949.641999999999</v>
       </c>
       <c r="G90">
         <v>482.1</v>
@@ -8673,37 +8673,37 @@
         <v>457.3</v>
       </c>
       <c r="M90">
-        <v>784.1770111999998</v>
+        <v>793.0881135999999</v>
       </c>
       <c r="N90">
-        <v>-326.8770111999998</v>
+        <v>-335.7881135999999</v>
       </c>
       <c r="O90">
-        <v>-62.10663212799997</v>
+        <v>-63.79974158399998</v>
       </c>
       <c r="P90">
-        <v>-264.7703790719999</v>
+        <v>-271.9883720159999</v>
       </c>
       <c r="Q90">
-        <v>-162.2703790719999</v>
+        <v>-169.488372016</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4401507729593095</v>
+        <v>0.4760008432283377</v>
       </c>
       <c r="T90">
-        <v>6.649320564935874</v>
+        <v>7.253804252657319</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1108002386693787</v>
+        <v>0.1095552921674755</v>
       </c>
       <c r="W90">
-        <v>0.1785513120751888</v>
+        <v>0.1788012973327709</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5831591508914666</v>
+        <v>0.57660680088145</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2114932473812833</v>
+        <v>0.2130432473812832</v>
       </c>
       <c r="C91">
-        <v>-2131.187302485489</v>
+        <v>-2187.565480581086</v>
       </c>
       <c r="D91">
-        <v>1336.35469751451</v>
+        <v>1324.354519418914</v>
       </c>
       <c r="E91">
-        <v>3936.741999999999</v>
+        <v>3981.119999999999</v>
       </c>
       <c r="F91">
-        <v>3949.641999999999</v>
+        <v>3994.02</v>
       </c>
       <c r="G91">
         <v>482.1</v>
@@ -8755,37 +8755,37 @@
         <v>457.3</v>
       </c>
       <c r="M91">
-        <v>793.0881135999999</v>
+        <v>801.9992159999999</v>
       </c>
       <c r="N91">
-        <v>-335.7881135999999</v>
+        <v>-344.6992159999999</v>
       </c>
       <c r="O91">
-        <v>-63.79974158399998</v>
+        <v>-65.49285103999999</v>
       </c>
       <c r="P91">
-        <v>-271.9883720159999</v>
+        <v>-279.2063649599999</v>
       </c>
       <c r="Q91">
-        <v>-169.488372016</v>
+        <v>-176.70636496</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4760008432283377</v>
+        <v>0.5190209275511715</v>
       </c>
       <c r="T91">
-        <v>7.253804252657319</v>
+        <v>7.979184677923051</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1095552921674755</v>
+        <v>0.1083380111433924</v>
       </c>
       <c r="W91">
-        <v>0.1788012973327709</v>
+        <v>0.1790457273624068</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.57660680088145</v>
+        <v>0.570200058649434</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2130432473812832</v>
+        <v>0.2145932473812833</v>
       </c>
       <c r="C92">
-        <v>-2187.565480581086</v>
+        <v>-2243.730058715827</v>
       </c>
       <c r="D92">
-        <v>1324.354519418914</v>
+        <v>1312.567941284173</v>
       </c>
       <c r="E92">
-        <v>3981.119999999999</v>
+        <v>4025.498</v>
       </c>
       <c r="F92">
-        <v>3994.02</v>
+        <v>4038.398</v>
       </c>
       <c r="G92">
         <v>482.1</v>
@@ -8837,37 +8837,37 @@
         <v>457.3</v>
       </c>
       <c r="M92">
-        <v>801.9992159999999</v>
+        <v>810.9103183999999</v>
       </c>
       <c r="N92">
-        <v>-344.6992159999999</v>
+        <v>-353.6103183999999</v>
       </c>
       <c r="O92">
-        <v>-65.49285103999999</v>
+        <v>-67.18596049599999</v>
       </c>
       <c r="P92">
-        <v>-279.2063649599999</v>
+        <v>-286.4243579039999</v>
       </c>
       <c r="Q92">
-        <v>-176.70636496</v>
+        <v>-183.924357904</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5190209275511715</v>
+        <v>0.5716010306124126</v>
       </c>
       <c r="T92">
-        <v>7.979184677923051</v>
+        <v>8.865760753247834</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1083380111433924</v>
+        <v>0.1071474835484101</v>
       </c>
       <c r="W92">
-        <v>0.1790457273624068</v>
+        <v>0.1792847853034793</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.570200058649434</v>
+        <v>0.5639341239390006</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2145932473812833</v>
+        <v>0.2161432473812833</v>
       </c>
       <c r="C93">
-        <v>-2243.730058715827</v>
+        <v>-2299.686689614483</v>
       </c>
       <c r="D93">
-        <v>1312.567941284173</v>
+        <v>1300.989310385516</v>
       </c>
       <c r="E93">
-        <v>4025.498</v>
+        <v>4069.875999999999</v>
       </c>
       <c r="F93">
-        <v>4038.398</v>
+        <v>4082.775999999999</v>
       </c>
       <c r="G93">
         <v>482.1</v>
@@ -8919,37 +8919,37 @@
         <v>457.3</v>
       </c>
       <c r="M93">
-        <v>810.9103183999999</v>
+        <v>819.8214207999999</v>
       </c>
       <c r="N93">
-        <v>-353.6103183999999</v>
+        <v>-362.5214207999999</v>
       </c>
       <c r="O93">
-        <v>-67.18596049599999</v>
+        <v>-68.87906995199998</v>
       </c>
       <c r="P93">
-        <v>-286.4243579039999</v>
+        <v>-293.642350848</v>
       </c>
       <c r="Q93">
-        <v>-183.924357904</v>
+        <v>-191.142350848</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5716010306124126</v>
+        <v>0.6373261594389645</v>
       </c>
       <c r="T93">
-        <v>8.865760753247834</v>
+        <v>9.973980847403817</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1071474835484101</v>
+        <v>0.1059828369881013</v>
       </c>
       <c r="W93">
-        <v>0.1792847853034793</v>
+        <v>0.1795186463327893</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5639341239390006</v>
+        <v>0.5578044052005332</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2161432473812833</v>
+        <v>0.2176932473812833</v>
       </c>
       <c r="C94">
-        <v>-2299.686689614483</v>
+        <v>-2355.440828287123</v>
       </c>
       <c r="D94">
-        <v>1300.989310385516</v>
+        <v>1289.613171712876</v>
       </c>
       <c r="E94">
-        <v>4069.875999999999</v>
+        <v>4114.254</v>
       </c>
       <c r="F94">
-        <v>4082.775999999999</v>
+        <v>4127.154</v>
       </c>
       <c r="G94">
         <v>482.1</v>
@@ -9001,37 +9001,37 @@
         <v>457.3</v>
       </c>
       <c r="M94">
-        <v>819.8214207999999</v>
+        <v>828.7325231999999</v>
       </c>
       <c r="N94">
-        <v>-362.5214207999999</v>
+        <v>-371.4325231999999</v>
       </c>
       <c r="O94">
-        <v>-68.87906995199998</v>
+        <v>-70.57217940799998</v>
       </c>
       <c r="P94">
-        <v>-293.642350848</v>
+        <v>-300.860343792</v>
       </c>
       <c r="Q94">
-        <v>-191.142350848</v>
+        <v>-198.360343792</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6373261594389645</v>
+        <v>0.7218298965016737</v>
       </c>
       <c r="T94">
-        <v>9.973980847403817</v>
+        <v>11.39883525417579</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1059828369881013</v>
+        <v>0.1048432365903798</v>
       </c>
       <c r="W94">
-        <v>0.1795186463327893</v>
+        <v>0.1797474780926518</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5578044052005332</v>
+        <v>0.55180650837042</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2176932473812833</v>
+        <v>0.2192432473812832</v>
       </c>
       <c r="C95">
-        <v>-2355.440828287123</v>
+        <v>-2410.997740598474</v>
       </c>
       <c r="D95">
-        <v>1289.613171712876</v>
+        <v>1278.434259401525</v>
       </c>
       <c r="E95">
-        <v>4114.254</v>
+        <v>4158.632</v>
       </c>
       <c r="F95">
-        <v>4127.154</v>
+        <v>4171.531999999999</v>
       </c>
       <c r="G95">
         <v>482.1</v>
@@ -9083,37 +9083,37 @@
         <v>457.3</v>
       </c>
       <c r="M95">
-        <v>828.7325231999999</v>
+        <v>837.6436255999998</v>
       </c>
       <c r="N95">
-        <v>-371.4325231999999</v>
+        <v>-380.3436255999998</v>
       </c>
       <c r="O95">
-        <v>-70.57217940799998</v>
+        <v>-72.26528886399997</v>
       </c>
       <c r="P95">
-        <v>-300.860343792</v>
+        <v>-308.0783367359999</v>
       </c>
       <c r="Q95">
-        <v>-198.360343792</v>
+        <v>-205.5783367359999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7218298965016737</v>
+        <v>0.8345015459186196</v>
       </c>
       <c r="T95">
-        <v>11.39883525417579</v>
+        <v>13.29864112987176</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1048432365903798</v>
+        <v>0.1037278830096311</v>
       </c>
       <c r="W95">
-        <v>0.1797474780926518</v>
+        <v>0.1799714410916661</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.55180650837042</v>
+        <v>0.5459362263664793</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2192432473812832</v>
+        <v>0.2207932473812833</v>
       </c>
       <c r="C96">
-        <v>-2410.997740598474</v>
+        <v>-2466.362511395437</v>
       </c>
       <c r="D96">
-        <v>1278.434259401525</v>
+        <v>1267.447488604563</v>
       </c>
       <c r="E96">
-        <v>4158.632</v>
+        <v>4203.01</v>
       </c>
       <c r="F96">
-        <v>4171.531999999999</v>
+        <v>4215.91</v>
       </c>
       <c r="G96">
         <v>482.1</v>
@@ -9165,37 +9165,37 @@
         <v>457.3</v>
       </c>
       <c r="M96">
-        <v>837.6436255999998</v>
+        <v>846.554728</v>
       </c>
       <c r="N96">
-        <v>-380.3436255999998</v>
+        <v>-389.2547279999999</v>
       </c>
       <c r="O96">
-        <v>-72.26528886399997</v>
+        <v>-73.95839831999999</v>
       </c>
       <c r="P96">
-        <v>-308.0783367359999</v>
+        <v>-315.29632968</v>
       </c>
       <c r="Q96">
-        <v>-205.5783367359999</v>
+        <v>-212.79632968</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8345015459186196</v>
+        <v>0.992241855102344</v>
       </c>
       <c r="T96">
-        <v>13.29864112987176</v>
+        <v>15.95836935584612</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1037278830096311</v>
+        <v>0.1026360105568981</v>
       </c>
       <c r="W96">
-        <v>0.1799714410916661</v>
+        <v>0.1801906890801749</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5459362263664793</v>
+        <v>0.5401895292468322</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2207932473812833</v>
+        <v>0.2223432473812832</v>
       </c>
       <c r="C97">
-        <v>-2466.362511395437</v>
+        <v>-2521.540052219073</v>
       </c>
       <c r="D97">
-        <v>1267.447488604563</v>
+        <v>1256.647947780927</v>
       </c>
       <c r="E97">
-        <v>4203.01</v>
+        <v>4247.388</v>
       </c>
       <c r="F97">
-        <v>4215.91</v>
+        <v>4260.288</v>
       </c>
       <c r="G97">
         <v>482.1</v>
@@ -9247,37 +9247,37 @@
         <v>457.3</v>
       </c>
       <c r="M97">
-        <v>846.554728</v>
+        <v>855.4658304</v>
       </c>
       <c r="N97">
-        <v>-389.2547279999999</v>
+        <v>-398.1658303999999</v>
       </c>
       <c r="O97">
-        <v>-73.95839831999999</v>
+        <v>-75.65150777599999</v>
       </c>
       <c r="P97">
-        <v>-315.29632968</v>
+        <v>-322.514322624</v>
       </c>
       <c r="Q97">
-        <v>-212.79632968</v>
+        <v>-220.014322624</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.992241855102344</v>
+        <v>1.228852318877931</v>
       </c>
       <c r="T97">
-        <v>15.95836935584612</v>
+        <v>19.94796169480766</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1026360105568981</v>
+        <v>0.1015668854469304</v>
       </c>
       <c r="W97">
-        <v>0.1801906890801749</v>
+        <v>0.1804053694022564</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5401895292468322</v>
+        <v>0.5345625549838443</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2223432473812832</v>
+        <v>0.2238932473812832</v>
       </c>
       <c r="C98">
-        <v>-2521.540052219073</v>
+        <v>-2576.535108625666</v>
       </c>
       <c r="D98">
-        <v>1256.647947780927</v>
+        <v>1246.030891374334</v>
       </c>
       <c r="E98">
-        <v>4247.388</v>
+        <v>4291.766</v>
       </c>
       <c r="F98">
-        <v>4260.288</v>
+        <v>4304.665999999999</v>
       </c>
       <c r="G98">
         <v>482.1</v>
@@ -9329,37 +9329,37 @@
         <v>457.3</v>
       </c>
       <c r="M98">
-        <v>855.4658304</v>
+        <v>864.3769327999998</v>
       </c>
       <c r="N98">
-        <v>-398.1658303999999</v>
+        <v>-407.0769327999998</v>
       </c>
       <c r="O98">
-        <v>-75.65150777599999</v>
+        <v>-77.34461723199998</v>
       </c>
       <c r="P98">
-        <v>-322.514322624</v>
+        <v>-329.7323155679999</v>
       </c>
       <c r="Q98">
-        <v>-220.014322624</v>
+        <v>-227.2323155679999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.228852318877927</v>
+        <v>1.623203091837237</v>
       </c>
       <c r="T98">
-        <v>19.94796169480761</v>
+        <v>26.59728225974348</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1015668854469304</v>
+        <v>0.1005198041536631</v>
       </c>
       <c r="W98">
-        <v>0.1804053694022564</v>
+        <v>0.1806156233259444</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5345625549838443</v>
+        <v>0.5290516008087531</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2238932473812832</v>
+        <v>0.2254432473812832</v>
       </c>
       <c r="C99">
-        <v>-2576.535108625666</v>
+        <v>-2631.35226713976</v>
       </c>
       <c r="D99">
-        <v>1246.030891374334</v>
+        <v>1235.591732860239</v>
       </c>
       <c r="E99">
-        <v>4291.766</v>
+        <v>4336.143999999999</v>
       </c>
       <c r="F99">
-        <v>4304.665999999999</v>
+        <v>4349.043999999999</v>
       </c>
       <c r="G99">
         <v>482.1</v>
@@ -9411,37 +9411,37 @@
         <v>457.3</v>
       </c>
       <c r="M99">
-        <v>864.3769327999998</v>
+        <v>873.2880351999999</v>
       </c>
       <c r="N99">
-        <v>-407.0769327999998</v>
+        <v>-415.9880351999998</v>
       </c>
       <c r="O99">
-        <v>-77.34461723199998</v>
+        <v>-79.03772668799998</v>
       </c>
       <c r="P99">
-        <v>-329.7323155679999</v>
+        <v>-336.9503085119999</v>
       </c>
       <c r="Q99">
-        <v>-227.2323155679999</v>
+        <v>-234.4503085119999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.623203091837237</v>
+        <v>2.411904637755855</v>
       </c>
       <c r="T99">
-        <v>26.59728225974348</v>
+        <v>39.89592338961521</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1005198041536631</v>
+        <v>0.09949409186638083</v>
       </c>
       <c r="W99">
-        <v>0.1806156233259444</v>
+        <v>0.1808215863532307</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5290516008087531</v>
+        <v>0.5236531150862149</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2254432473812832</v>
+        <v>0.2269932473812833</v>
       </c>
       <c r="C100">
-        <v>-2631.35226713976</v>
+        <v>-2685.995961860601</v>
       </c>
       <c r="D100">
-        <v>1235.591732860239</v>
+        <v>1225.326038139399</v>
       </c>
       <c r="E100">
-        <v>4336.143999999999</v>
+        <v>4380.522</v>
       </c>
       <c r="F100">
-        <v>4349.043999999999</v>
+        <v>4393.422</v>
       </c>
       <c r="G100">
         <v>482.1</v>
@@ -9493,37 +9493,37 @@
         <v>457.3</v>
       </c>
       <c r="M100">
-        <v>873.2880351999999</v>
+        <v>882.1991376</v>
       </c>
       <c r="N100">
-        <v>-415.9880351999998</v>
+        <v>-424.8991376</v>
       </c>
       <c r="O100">
-        <v>-79.03772668799998</v>
+        <v>-80.73083614399999</v>
       </c>
       <c r="P100">
-        <v>-336.9503085119999</v>
+        <v>-344.168301456</v>
       </c>
       <c r="Q100">
-        <v>-234.4503085119999</v>
+        <v>-241.6683014560001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.411904637755855</v>
+        <v>4.778009275511709</v>
       </c>
       <c r="T100">
-        <v>39.89592338961521</v>
+        <v>79.79184677923043</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09949409186638083</v>
+        <v>0.09848910103944768</v>
       </c>
       <c r="W100">
-        <v>0.1808215863532307</v>
+        <v>0.1810233885112789</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5236531150862149</v>
+        <v>0.5183636896813035</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2269932473812833</v>
-      </c>
-      <c r="C101">
-        <v>-2685.995961860601</v>
-      </c>
-      <c r="D101">
-        <v>1225.326038139399</v>
-      </c>
-      <c r="E101">
-        <v>4380.522</v>
-      </c>
-      <c r="F101">
-        <v>4393.422</v>
-      </c>
-      <c r="G101">
-        <v>482.1</v>
-      </c>
-      <c r="H101">
-        <v>4424.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>559.8</v>
-      </c>
-      <c r="K101">
-        <v>102.4999999999999</v>
-      </c>
-      <c r="L101">
-        <v>457.3</v>
-      </c>
-      <c r="M101">
-        <v>882.1991376</v>
-      </c>
-      <c r="N101">
-        <v>-424.8991376</v>
-      </c>
-      <c r="O101">
-        <v>-80.73083614399999</v>
-      </c>
-      <c r="P101">
-        <v>-344.168301456</v>
-      </c>
-      <c r="Q101">
-        <v>-241.6683014560001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.778009275511709</v>
-      </c>
-      <c r="T101">
-        <v>79.79184677923043</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09848910103944768</v>
-      </c>
-      <c r="W101">
-        <v>0.1810233885112789</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5183636896813035</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
